--- a/data/vendas-espelho.xlsx
+++ b/data/vendas-espelho.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30021"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Dropbox\SPE JARDIM LUZ\Gerenciamento de Obra - Ramon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743A2C4A-30D6-4933-AFF8-A76FBA531B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E61F6E-858B-4E35-B93D-350FA07312D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1062,7 +1062,7 @@
         <v>1</v>
       </c>
       <c r="T2" s="1">
-        <v>359744.09710174106</v>
+        <v>330315.8</v>
       </c>
       <c r="U2" t="s">
         <v>1</v>
@@ -1127,7 +1127,7 @@
         <v>1</v>
       </c>
       <c r="T3" s="1">
-        <v>359429.32437311817</v>
+        <v>297369</v>
       </c>
       <c r="U3" t="s">
         <v>1</v>
@@ -1517,7 +1517,7 @@
         <v>1</v>
       </c>
       <c r="T9" s="1">
-        <v>383699.83449575113</v>
+        <v>337748.12</v>
       </c>
       <c r="U9" t="s">
         <v>1</v>
@@ -1582,7 +1582,7 @@
         <v>1</v>
       </c>
       <c r="T10" s="1">
-        <v>361317.96074485511</v>
+        <v>351450</v>
       </c>
       <c r="U10" t="s">
         <v>1</v>
@@ -1647,7 +1647,7 @@
         <v>1</v>
       </c>
       <c r="T11" s="1">
-        <v>361003.18801623239</v>
+        <v>297440.3</v>
       </c>
       <c r="U11" t="s">
         <v>1</v>
@@ -1712,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="T12" s="1">
-        <v>361317.96074485511</v>
+        <v>331760.92</v>
       </c>
       <c r="U12" t="s">
         <v>1</v>
@@ -1777,7 +1777,7 @@
         <v>1</v>
       </c>
       <c r="T13" s="1">
-        <v>360531.028923298</v>
+        <v>331038.36</v>
       </c>
       <c r="U13" t="s">
         <v>1</v>
@@ -1842,7 +1842,7 @@
         <v>1</v>
       </c>
       <c r="T14" s="1">
-        <v>361317.96074485511</v>
+        <v>297708.18</v>
       </c>
       <c r="U14" t="s">
         <v>1</v>
@@ -1907,7 +1907,7 @@
         <v>1</v>
       </c>
       <c r="T15" s="1">
-        <v>360531.02892329806</v>
+        <v>312549.92</v>
       </c>
       <c r="U15" t="s">
         <v>1</v>
@@ -1972,7 +1972,7 @@
         <v>1</v>
       </c>
       <c r="T16" s="1">
-        <v>361317.96074485511</v>
+        <v>301440</v>
       </c>
       <c r="U16" t="s">
         <v>1</v>
@@ -2037,7 +2037,7 @@
         <v>1</v>
       </c>
       <c r="T17" s="1">
-        <v>360531.02892329806</v>
+        <v>298038.75</v>
       </c>
       <c r="U17" t="s">
         <v>1</v>
@@ -2167,7 +2167,7 @@
         <v>1</v>
       </c>
       <c r="T19" s="1">
-        <v>376741.82444737392</v>
+        <v>332171.26</v>
       </c>
       <c r="U19" t="s">
         <v>1</v>
@@ -2232,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="T20" s="1">
-        <v>376741.82444737392</v>
+        <v>332171.26</v>
       </c>
       <c r="U20" t="s">
         <v>1</v>
@@ -2246,61 +2246,61 @@
         <v>366249.40015994618</v>
       </c>
       <c r="C21" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="1">
         <v>366249.40015994618</v>
       </c>
       <c r="E21" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="1">
         <v>366249.40015994618</v>
       </c>
       <c r="G21" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" s="1">
         <v>366249.40015994618</v>
       </c>
       <c r="I21" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" s="1">
         <v>366249.40015994618</v>
       </c>
       <c r="K21" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" s="1">
         <v>366249.40015994618</v>
       </c>
       <c r="M21" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N21" s="1">
         <v>366249.40015994618</v>
       </c>
       <c r="O21" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P21" s="1">
         <v>366249.40015994618</v>
       </c>
       <c r="Q21" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21" s="1">
         <v>366249.40015994618</v>
       </c>
       <c r="S21" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T21" s="1">
         <v>366249.40015994618</v>
       </c>
       <c r="U21" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.3">
@@ -2362,7 +2362,7 @@
         <v>1</v>
       </c>
       <c r="T22" s="1">
-        <v>374643.33958988829</v>
+        <v>330268.78999999998</v>
       </c>
       <c r="U22" t="s">
         <v>1</v>
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="T24" s="1">
-        <v>374643.33958988829</v>
+        <v>312960</v>
       </c>
       <c r="U24" t="s">
         <v>1</v>
@@ -2557,7 +2557,7 @@
         <v>1</v>
       </c>
       <c r="T25" s="1">
-        <v>366249.40015994618</v>
+        <v>302905.59999999998</v>
       </c>
       <c r="U25" t="s">
         <v>1</v>
@@ -2752,7 +2752,7 @@
         <v>1</v>
       </c>
       <c r="T28" s="1">
-        <v>377161.52141887089</v>
+        <v>325123.86</v>
       </c>
       <c r="U28" t="s">
         <v>1</v>
@@ -3012,7 +3012,7 @@
         <v>1</v>
       </c>
       <c r="T32" s="1">
-        <v>375063.03656138532</v>
+        <v>323268</v>
       </c>
       <c r="U32" t="s">
         <v>1</v>
@@ -3077,7 +3077,7 @@
         <v>1</v>
       </c>
       <c r="T33" s="1">
-        <v>366669.09713144321</v>
+        <v>303262.8</v>
       </c>
       <c r="U33" t="s">
         <v>1</v>
@@ -3142,7 +3142,7 @@
         <v>1</v>
       </c>
       <c r="T34" s="1">
-        <v>377581.21839036816</v>
+        <v>329000</v>
       </c>
       <c r="U34" t="s">
         <v>1</v>
@@ -3207,7 +3207,7 @@
         <v>1</v>
       </c>
       <c r="T35" s="1">
-        <v>377581.21839036816</v>
+        <v>325500</v>
       </c>
       <c r="U35" t="s">
         <v>1</v>
@@ -3337,7 +3337,7 @@
         <v>1</v>
       </c>
       <c r="T37" s="1">
-        <v>367088.79410294036</v>
+        <v>303620</v>
       </c>
       <c r="U37" t="s">
         <v>1</v>
@@ -3402,7 +3402,7 @@
         <v>1</v>
       </c>
       <c r="T38" s="1">
-        <v>375482.73353288253</v>
+        <v>310764</v>
       </c>
       <c r="U38" t="s">
         <v>1</v>
@@ -3467,7 +3467,7 @@
         <v>1</v>
       </c>
       <c r="T39" s="1">
-        <v>367088.79410294036</v>
+        <v>323419.90000000002</v>
       </c>
       <c r="U39" t="s">
         <v>1</v>
@@ -3532,7 +3532,7 @@
         <v>1</v>
       </c>
       <c r="T40" s="1">
-        <v>375482.73353288253</v>
+        <v>309763.71999999997</v>
       </c>
       <c r="U40" t="s">
         <v>1</v>
@@ -3597,7 +3597,7 @@
         <v>1</v>
       </c>
       <c r="T41" s="1">
-        <v>367088.79410294036</v>
+        <v>303620</v>
       </c>
       <c r="U41" t="s">
         <v>1</v>
@@ -3662,7 +3662,7 @@
         <v>1</v>
       </c>
       <c r="T42" s="1">
-        <v>378000.91536186513</v>
+        <v>311260.31</v>
       </c>
       <c r="U42" t="s">
         <v>1</v>
@@ -3727,7 +3727,7 @@
         <v>1</v>
       </c>
       <c r="T43" s="1">
-        <v>378000.91536186513</v>
+        <v>312906.25</v>
       </c>
       <c r="U43" t="s">
         <v>1</v>
@@ -3792,7 +3792,7 @@
         <v>1</v>
       </c>
       <c r="T44" s="1">
-        <v>378000.91536186513</v>
+        <v>312907.2</v>
       </c>
       <c r="U44" t="s">
         <v>1</v>
@@ -3857,7 +3857,7 @@
         <v>1</v>
       </c>
       <c r="T45" s="1">
-        <v>367508.49107443745</v>
+        <v>302977.2</v>
       </c>
       <c r="U45" t="s">
         <v>1</v>
@@ -3987,7 +3987,7 @@
         <v>1</v>
       </c>
       <c r="T47" s="1">
-        <v>367508.49107443745</v>
+        <v>323380</v>
       </c>
       <c r="U47" t="s">
         <v>1</v>
@@ -4052,7 +4052,7 @@
         <v>1</v>
       </c>
       <c r="T48" s="1">
-        <v>375902.43050437962</v>
+        <v>311121.2</v>
       </c>
       <c r="U48" t="s">
         <v>1</v>
@@ -4182,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="T50" s="1">
-        <v>378420.61233336222</v>
+        <v>311615.64</v>
       </c>
       <c r="U50" t="s">
         <v>1</v>
@@ -4312,7 +4312,7 @@
         <v>1</v>
       </c>
       <c r="T52" s="1">
-        <v>378420.61233336222</v>
+        <v>311615.64</v>
       </c>
       <c r="U52" t="s">
         <v>1</v>
@@ -4442,7 +4442,7 @@
         <v>1</v>
       </c>
       <c r="T54" s="1">
-        <v>376322.12747587671</v>
+        <v>312314.15999999997</v>
       </c>
       <c r="U54" t="s">
         <v>1</v>
@@ -4637,7 +4637,7 @@
         <v>1</v>
       </c>
       <c r="T57" s="1">
-        <v>367928.18804593454</v>
+        <v>303570.15000000002</v>
       </c>
       <c r="U57" t="s">
         <v>1</v>
@@ -4702,7 +4702,7 @@
         <v>1</v>
       </c>
       <c r="T58" s="1">
-        <v>378840.30930485943</v>
+        <v>311970.98</v>
       </c>
       <c r="U58" t="s">
         <v>1</v>
@@ -4832,7 +4832,7 @@
         <v>1</v>
       </c>
       <c r="T60" s="1">
-        <v>378840.30930485943</v>
+        <v>312621.65000000002</v>
       </c>
       <c r="U60" t="s">
         <v>1</v>
@@ -4962,7 +4962,7 @@
         <v>1</v>
       </c>
       <c r="T62" s="1">
-        <v>376741.82444737392</v>
+        <v>311835.59999999998</v>
       </c>
       <c r="U62" t="s">
         <v>1</v>
@@ -4976,61 +4976,61 @@
         <v>368347.88501743157</v>
       </c>
       <c r="C63" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" s="1">
         <v>368347.88501743157</v>
       </c>
       <c r="E63" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="1">
         <v>368347.88501743163</v>
       </c>
       <c r="G63" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" s="1">
         <v>368347.88501743157</v>
       </c>
       <c r="I63" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J63" s="1">
         <v>368347.88501743157</v>
       </c>
       <c r="K63" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L63" s="1">
         <v>368347.88501743157</v>
       </c>
       <c r="M63" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N63" s="1">
         <v>368347.88501743157</v>
       </c>
       <c r="O63" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P63" s="1">
         <v>368347.88501743157</v>
       </c>
       <c r="Q63" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R63" s="1">
         <v>368347.88501743157</v>
       </c>
       <c r="S63" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T63" s="1">
         <v>368347.88501743157</v>
       </c>
       <c r="U63" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.3">
@@ -5092,7 +5092,7 @@
         <v>1</v>
       </c>
       <c r="T64" s="1">
-        <v>376741.82444737392</v>
+        <v>332171.27</v>
       </c>
       <c r="U64" t="s">
         <v>1</v>
@@ -5157,7 +5157,7 @@
         <v>1</v>
       </c>
       <c r="T65" s="1">
-        <v>368347.88501743157</v>
+        <v>304691.59999999998</v>
       </c>
       <c r="U65" t="s">
         <v>1</v>
@@ -5287,7 +5287,7 @@
         <v>1</v>
       </c>
       <c r="T67" s="1">
-        <v>395513.6720639299</v>
+        <v>290000</v>
       </c>
       <c r="U67" t="s">
         <v>1</v>
@@ -5352,7 +5352,7 @@
         <v>1</v>
       </c>
       <c r="T68" s="1">
-        <v>382407.73356258462</v>
+        <v>338158.2</v>
       </c>
       <c r="U68" t="s">
         <v>1</v>
@@ -5612,7 +5612,7 @@
         <v>1</v>
       </c>
       <c r="T72" s="1">
-        <v>380309.24870509928</v>
+        <v>311121.2</v>
       </c>
       <c r="U72" t="s">
         <v>1</v>
@@ -5677,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="T73" s="1">
-        <v>371915.30927515705</v>
+        <v>307727.76</v>
       </c>
       <c r="U73" t="s">
         <v>1</v>
@@ -5742,7 +5742,7 @@
         <v>1</v>
       </c>
       <c r="T74" s="1">
-        <v>383037.2790198304</v>
+        <v>320387.5</v>
       </c>
       <c r="U74" t="s">
         <v>1</v>
@@ -5807,7 +5807,7 @@
         <v>1</v>
       </c>
       <c r="T75" s="1">
-        <v>383037.2790198304</v>
+        <v>274525</v>
       </c>
       <c r="U75" t="s">
         <v>1</v>
@@ -5872,7 +5872,7 @@
         <v>1</v>
       </c>
       <c r="T76" s="1">
-        <v>383037.2790198304</v>
+        <v>360355.93</v>
       </c>
       <c r="U76" t="s">
         <v>1</v>
@@ -5937,7 +5937,7 @@
         <v>1</v>
       </c>
       <c r="T77" s="1">
-        <v>372544.85473240277</v>
+        <v>310493</v>
       </c>
       <c r="U77" t="s">
         <v>1</v>
@@ -6002,7 +6002,7 @@
         <v>1</v>
       </c>
       <c r="T78" s="1">
-        <v>380938.79416234483</v>
+        <v>347641.85</v>
       </c>
       <c r="U78" t="s">
         <v>1</v>
@@ -6262,7 +6262,7 @@
         <v>1</v>
       </c>
       <c r="T82" s="1">
-        <v>383666.82447707601</v>
+        <v>274525</v>
       </c>
       <c r="U82" t="s">
         <v>1</v>
@@ -6327,7 +6327,7 @@
         <v>1</v>
       </c>
       <c r="T83" s="1">
-        <v>408086.53224855912</v>
+        <v>338400</v>
       </c>
       <c r="U83" t="s">
         <v>1</v>
@@ -6652,7 +6652,7 @@
         <v>1</v>
       </c>
       <c r="T88" s="1">
-        <v>405165.70088834345</v>
+        <v>357200</v>
       </c>
       <c r="U88" t="s">
         <v>1</v>
@@ -6782,7 +6782,7 @@
         <v>1</v>
       </c>
       <c r="T90" s="1">
-        <v>384086.52144857321</v>
+        <v>358027</v>
       </c>
       <c r="U90" t="s">
         <v>1</v>
@@ -6847,7 +6847,7 @@
         <v>1</v>
       </c>
       <c r="T91" s="1">
-        <v>410861.57995273953</v>
+        <v>338400</v>
       </c>
       <c r="U91" t="s">
         <v>1</v>
@@ -6977,7 +6977,7 @@
         <v>1</v>
       </c>
       <c r="T93" s="1">
-        <v>373594.09716114553</v>
+        <v>312445.5</v>
       </c>
       <c r="U93" t="s">
         <v>1</v>
@@ -7107,7 +7107,7 @@
         <v>1</v>
       </c>
       <c r="T95" s="1">
-        <v>373594.09716114553</v>
+        <v>312445.5</v>
       </c>
       <c r="U95" t="s">
         <v>1</v>
@@ -7172,7 +7172,7 @@
         <v>1</v>
       </c>
       <c r="T96" s="1">
-        <v>381988.0365910877</v>
+        <v>336490</v>
       </c>
       <c r="U96" t="s">
         <v>1</v>
@@ -7302,7 +7302,7 @@
         <v>1</v>
       </c>
       <c r="T98" s="1">
-        <v>384506.21842007025</v>
+        <v>264000</v>
       </c>
       <c r="U98" t="s">
         <v>1</v>
@@ -7367,7 +7367,7 @@
         <v>1</v>
       </c>
       <c r="T99" s="1">
-        <v>384506.21842007025</v>
+        <v>296695.15000000002</v>
       </c>
       <c r="U99" t="s">
         <v>1</v>
@@ -7497,7 +7497,7 @@
         <v>1</v>
       </c>
       <c r="T101" s="1">
-        <v>374013.79413264262</v>
+        <v>311806.5</v>
       </c>
       <c r="U101" t="s">
         <v>1</v>
@@ -7627,7 +7627,7 @@
         <v>1</v>
       </c>
       <c r="T103" s="1">
-        <v>374013.79413264262</v>
+        <v>329270</v>
       </c>
       <c r="U103" t="s">
         <v>1</v>
@@ -7757,7 +7757,7 @@
         <v>1</v>
       </c>
       <c r="T105" s="1">
-        <v>374013.79413264262</v>
+        <v>312806.5</v>
       </c>
       <c r="U105" t="s">
         <v>1</v>
@@ -7822,7 +7822,7 @@
         <v>1</v>
       </c>
       <c r="T106" s="1">
-        <v>384925.9153915674</v>
+        <v>264000</v>
       </c>
       <c r="U106" t="s">
         <v>1</v>
@@ -7887,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="T107" s="1">
-        <v>384925.9153915674</v>
+        <v>370782.5</v>
       </c>
       <c r="U107" t="s">
         <v>1</v>
@@ -8147,7 +8147,7 @@
         <v>1</v>
       </c>
       <c r="T111" s="1">
-        <v>374433.49110413966</v>
+        <v>322710</v>
       </c>
       <c r="U111" t="s">
         <v>1</v>
@@ -8212,7 +8212,7 @@
         <v>1</v>
       </c>
       <c r="T112" s="1">
-        <v>382827.43053408188</v>
+        <v>336688.35</v>
       </c>
       <c r="U112" t="s">
         <v>1</v>
@@ -8342,7 +8342,7 @@
         <v>1</v>
       </c>
       <c r="T114" s="1">
-        <v>385345.61236306443</v>
+        <v>330407</v>
       </c>
       <c r="U114" t="s">
         <v>1</v>
@@ -8472,7 +8472,7 @@
         <v>1</v>
       </c>
       <c r="T116" s="1">
-        <v>385345.61236306443</v>
+        <v>318801.02</v>
       </c>
       <c r="U116" t="s">
         <v>1</v>
@@ -8602,7 +8602,7 @@
         <v>1</v>
       </c>
       <c r="T118" s="1">
-        <v>383247.12750557903</v>
+        <v>319060.34000000003</v>
       </c>
       <c r="U118" t="s">
         <v>1</v>
@@ -8667,7 +8667,7 @@
         <v>1</v>
       </c>
       <c r="T119" s="1">
-        <v>374853.1880756368</v>
+        <v>313528.5</v>
       </c>
       <c r="U119" t="s">
         <v>1</v>
@@ -8732,7 +8732,7 @@
         <v>1</v>
       </c>
       <c r="T120" s="1">
-        <v>383247.12750557903</v>
+        <v>319060.34999999998</v>
       </c>
       <c r="U120" t="s">
         <v>1</v>
@@ -8797,10 +8797,10 @@
         <v>2</v>
       </c>
       <c r="T121" s="1">
-        <v>404542.73719803535</v>
+        <v>347800</v>
       </c>
       <c r="U121" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/vendas-espelho.xlsx
+++ b/data/vendas-espelho.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30021"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30030"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Dropbox\SPE JARDIM LUZ\Gerenciamento de Obra - Ramon\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E61F6E-858B-4E35-B93D-350FA07312D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE28839-4066-4820-8378-47397387B5F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="91">
   <si>
     <t>Und</t>
   </si>
@@ -672,7 +672,7 @@
     <col min="19" max="19" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -1067,6 +1067,12 @@
       <c r="U2" t="s">
         <v>1</v>
       </c>
+      <c r="V2" s="1">
+        <v>330315.8</v>
+      </c>
+      <c r="W2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -1132,6 +1138,12 @@
       <c r="U3" t="s">
         <v>1</v>
       </c>
+      <c r="V3" s="1">
+        <v>297369</v>
+      </c>
+      <c r="W3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -1197,6 +1209,12 @@
       <c r="U4" t="s">
         <v>2</v>
       </c>
+      <c r="V4" s="1">
+        <v>390582.10689519066</v>
+      </c>
+      <c r="W4" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -1262,6 +1280,12 @@
       <c r="U5" t="s">
         <v>2</v>
       </c>
+      <c r="V5" s="1">
+        <v>390582.10689519066</v>
+      </c>
+      <c r="W5" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -1327,6 +1351,12 @@
       <c r="U6" t="s">
         <v>2</v>
       </c>
+      <c r="V6" s="1">
+        <v>384822.2206716598</v>
+      </c>
+      <c r="W6" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -1392,6 +1422,12 @@
       <c r="U7" t="s">
         <v>2</v>
       </c>
+      <c r="V7" s="1">
+        <v>390582.10689519066</v>
+      </c>
+      <c r="W7" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -1457,6 +1493,12 @@
       <c r="U8" t="s">
         <v>2</v>
       </c>
+      <c r="V8" s="1">
+        <v>384822.2206716598</v>
+      </c>
+      <c r="W8" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -1522,6 +1564,12 @@
       <c r="U9" t="s">
         <v>1</v>
       </c>
+      <c r="V9" s="1">
+        <v>337748.12</v>
+      </c>
+      <c r="W9" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -1587,6 +1635,12 @@
       <c r="U10" t="s">
         <v>1</v>
       </c>
+      <c r="V10" s="1">
+        <v>351814.23</v>
+      </c>
+      <c r="W10" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -1652,6 +1706,12 @@
       <c r="U11" t="s">
         <v>1</v>
       </c>
+      <c r="V11" s="1">
+        <v>297440.3</v>
+      </c>
+      <c r="W11" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -1717,6 +1777,12 @@
       <c r="U12" t="s">
         <v>1</v>
       </c>
+      <c r="V12" s="1">
+        <v>331760.92</v>
+      </c>
+      <c r="W12" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A13">
@@ -1782,6 +1848,12 @@
       <c r="U13" t="s">
         <v>1</v>
       </c>
+      <c r="V13" s="1">
+        <v>331038.36</v>
+      </c>
+      <c r="W13" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -1847,6 +1919,12 @@
       <c r="U14" t="s">
         <v>1</v>
       </c>
+      <c r="V14" s="1">
+        <v>297708.18</v>
+      </c>
+      <c r="W14" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -1912,6 +1990,12 @@
       <c r="U15" t="s">
         <v>1</v>
       </c>
+      <c r="V15" s="1">
+        <v>312549.92</v>
+      </c>
+      <c r="W15" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -1977,8 +2061,14 @@
       <c r="U16" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V16" s="1">
+        <v>301440</v>
+      </c>
+      <c r="W16" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>208</v>
       </c>
@@ -2042,8 +2132,14 @@
       <c r="U17" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V17" s="1">
+        <v>298038.75</v>
+      </c>
+      <c r="W17" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>301</v>
       </c>
@@ -2107,8 +2203,14 @@
       <c r="U18" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V18" s="1">
+        <v>376741.82444737392</v>
+      </c>
+      <c r="W18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>302</v>
       </c>
@@ -2172,8 +2274,14 @@
       <c r="U19" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V19" s="1">
+        <v>332171.26</v>
+      </c>
+      <c r="W19" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>303</v>
       </c>
@@ -2237,8 +2345,14 @@
       <c r="U20" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V20" s="1">
+        <v>332171.26</v>
+      </c>
+      <c r="W20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>304</v>
       </c>
@@ -2302,8 +2416,14 @@
       <c r="U21" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V21" s="1">
+        <v>366249.40015994618</v>
+      </c>
+      <c r="W21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>305</v>
       </c>
@@ -2367,8 +2487,14 @@
       <c r="U22" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V22" s="1">
+        <v>330268.78999999998</v>
+      </c>
+      <c r="W22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>306</v>
       </c>
@@ -2432,8 +2558,14 @@
       <c r="U23" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V23" s="1">
+        <v>366249.40015994618</v>
+      </c>
+      <c r="W23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>307</v>
       </c>
@@ -2497,8 +2629,14 @@
       <c r="U24" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V24" s="1">
+        <v>312960</v>
+      </c>
+      <c r="W24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>308</v>
       </c>
@@ -2562,8 +2700,14 @@
       <c r="U25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V25" s="1">
+        <v>302905.59999999998</v>
+      </c>
+      <c r="W25" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>401</v>
       </c>
@@ -2627,8 +2771,14 @@
       <c r="U26" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V26" s="1">
+        <v>340000</v>
+      </c>
+      <c r="W26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>402</v>
       </c>
@@ -2692,8 +2842,14 @@
       <c r="U27" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V27" s="1">
+        <v>377161.52141887089</v>
+      </c>
+      <c r="W27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>403</v>
       </c>
@@ -2757,8 +2913,14 @@
       <c r="U28" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V28" s="1">
+        <v>325123.86</v>
+      </c>
+      <c r="W28" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>404</v>
       </c>
@@ -2822,8 +2984,14 @@
       <c r="U29" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V29" s="1">
+        <v>396280.28959710058</v>
+      </c>
+      <c r="W29" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>405</v>
       </c>
@@ -2887,8 +3055,14 @@
       <c r="U30" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V30" s="1">
+        <v>375063.03656138532</v>
+      </c>
+      <c r="W30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>406</v>
       </c>
@@ -2952,8 +3126,14 @@
       <c r="U31" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V31" s="1">
+        <v>392229.96943265648</v>
+      </c>
+      <c r="W31" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>407</v>
       </c>
@@ -3017,8 +3197,14 @@
       <c r="U32" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V32" s="1">
+        <v>323268</v>
+      </c>
+      <c r="W32" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>408</v>
       </c>
@@ -3082,8 +3268,14 @@
       <c r="U33" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V33" s="1">
+        <v>303262.8</v>
+      </c>
+      <c r="W33" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>501</v>
       </c>
@@ -3147,8 +3339,14 @@
       <c r="U34" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V34" s="1">
+        <v>329000</v>
+      </c>
+      <c r="W34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>502</v>
       </c>
@@ -3212,8 +3410,14 @@
       <c r="U35" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V35" s="1">
+        <v>325500</v>
+      </c>
+      <c r="W35" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>503</v>
       </c>
@@ -3277,8 +3481,14 @@
       <c r="U36" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V36" s="1">
+        <v>377581.21839036816</v>
+      </c>
+      <c r="W36" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>504</v>
       </c>
@@ -3342,8 +3552,14 @@
       <c r="U37" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V37" s="1">
+        <v>303620</v>
+      </c>
+      <c r="W37" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>505</v>
       </c>
@@ -3407,8 +3623,14 @@
       <c r="U38" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V38" s="1">
+        <v>310764</v>
+      </c>
+      <c r="W38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>506</v>
       </c>
@@ -3472,8 +3694,14 @@
       <c r="U39" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V39" s="1">
+        <v>323419.90000000002</v>
+      </c>
+      <c r="W39" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>507</v>
       </c>
@@ -3537,8 +3765,14 @@
       <c r="U40" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V40" s="1">
+        <v>309763.71999999997</v>
+      </c>
+      <c r="W40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>508</v>
       </c>
@@ -3602,8 +3836,14 @@
       <c r="U41" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V41" s="1">
+        <v>303620</v>
+      </c>
+      <c r="W41" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>601</v>
       </c>
@@ -3667,8 +3907,14 @@
       <c r="U42" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V42" s="1">
+        <v>311260.31</v>
+      </c>
+      <c r="W42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>602</v>
       </c>
@@ -3732,8 +3978,14 @@
       <c r="U43" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V43" s="1">
+        <v>312906.25</v>
+      </c>
+      <c r="W43" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>603</v>
       </c>
@@ -3797,8 +4049,14 @@
       <c r="U44" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V44" s="1">
+        <v>312907.2</v>
+      </c>
+      <c r="W44" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>604</v>
       </c>
@@ -3862,8 +4120,14 @@
       <c r="U45" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V45" s="1">
+        <v>302977.2</v>
+      </c>
+      <c r="W45" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>605</v>
       </c>
@@ -3927,8 +4191,14 @@
       <c r="U46" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V46" s="1">
+        <v>402106.96778065222</v>
+      </c>
+      <c r="W46" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>606</v>
       </c>
@@ -3992,8 +4262,14 @@
       <c r="U47" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V47" s="1">
+        <v>323380</v>
+      </c>
+      <c r="W47" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>607</v>
       </c>
@@ -4057,8 +4333,14 @@
       <c r="U48" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V48" s="1">
+        <v>311121.2</v>
+      </c>
+      <c r="W48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>608</v>
       </c>
@@ -4122,8 +4404,14 @@
       <c r="U49" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V49" s="1">
+        <v>367508.49107443745</v>
+      </c>
+      <c r="W49" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>701</v>
       </c>
@@ -4187,8 +4475,14 @@
       <c r="U50" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V50" s="1">
+        <v>311615.64</v>
+      </c>
+      <c r="W50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>702</v>
       </c>
@@ -4252,8 +4546,14 @@
       <c r="U51" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V51" s="1">
+        <v>404800.69460283295</v>
+      </c>
+      <c r="W51" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>703</v>
       </c>
@@ -4317,8 +4617,14 @@
       <c r="U52" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V52" s="1">
+        <v>311615.64</v>
+      </c>
+      <c r="W52" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>704</v>
       </c>
@@ -4382,8 +4688,14 @@
       <c r="U53" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V53" s="1">
+        <v>393576.83284374687</v>
+      </c>
+      <c r="W53" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>705</v>
       </c>
@@ -4447,8 +4759,14 @@
       <c r="U54" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V54" s="1">
+        <v>312314.15999999997</v>
+      </c>
+      <c r="W54" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>706</v>
       </c>
@@ -4512,8 +4830,14 @@
       <c r="U55" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V55" s="1">
+        <v>393576.83284374687</v>
+      </c>
+      <c r="W55" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>707</v>
       </c>
@@ -4577,8 +4901,14 @@
       <c r="U56" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V56" s="1">
+        <v>376322.12747587671</v>
+      </c>
+      <c r="W56" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>708</v>
       </c>
@@ -4642,8 +4972,14 @@
       <c r="U57" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V57" s="1">
+        <v>303570.15000000002</v>
+      </c>
+      <c r="W57" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>801</v>
       </c>
@@ -4707,8 +5043,14 @@
       <c r="U58" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V58" s="1">
+        <v>311970.98</v>
+      </c>
+      <c r="W58" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>802</v>
       </c>
@@ -4772,8 +5114,14 @@
       <c r="U59" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V59" s="1">
+        <v>405249.64907319646</v>
+      </c>
+      <c r="W59" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>803</v>
       </c>
@@ -4837,8 +5185,14 @@
       <c r="U60" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V60" s="1">
+        <v>312621.65000000002</v>
+      </c>
+      <c r="W60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>804</v>
       </c>
@@ -4902,8 +5256,14 @@
       <c r="U61" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V61" s="1">
+        <v>368347.88501743157</v>
+      </c>
+      <c r="W61" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>805</v>
       </c>
@@ -4967,8 +5327,14 @@
       <c r="U62" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V62" s="1">
+        <v>311835.59999999998</v>
+      </c>
+      <c r="W62" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>806</v>
       </c>
@@ -5032,8 +5398,14 @@
       <c r="U63" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V63" s="1">
+        <v>368347.88501743157</v>
+      </c>
+      <c r="W63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>807</v>
       </c>
@@ -5097,8 +5469,14 @@
       <c r="U64" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V64" s="1">
+        <v>332171.27</v>
+      </c>
+      <c r="W64" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>808</v>
       </c>
@@ -5162,8 +5540,14 @@
       <c r="U65" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V65" s="1">
+        <v>304691.59999999998</v>
+      </c>
+      <c r="W65" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>901</v>
       </c>
@@ -5227,8 +5611,14 @@
       <c r="U66" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V66" s="1">
+        <v>382407.73356258462</v>
+      </c>
+      <c r="W66" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>902</v>
       </c>
@@ -5292,8 +5682,14 @@
       <c r="U67" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V67" s="1">
+        <v>290000</v>
+      </c>
+      <c r="W67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>903</v>
       </c>
@@ -5357,8 +5753,14 @@
       <c r="U68" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V68" s="1">
+        <v>338158.2</v>
+      </c>
+      <c r="W68" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>904</v>
       </c>
@@ -5422,8 +5824,14 @@
       <c r="U69" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V69" s="1">
+        <v>371915.30927515705</v>
+      </c>
+      <c r="W69" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>905</v>
       </c>
@@ -5487,8 +5895,14 @@
       <c r="U70" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V70" s="1">
+        <v>406820.98971946858</v>
+      </c>
+      <c r="W70" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>906</v>
       </c>
@@ -5552,8 +5966,14 @@
       <c r="U71" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V71" s="1">
+        <v>397841.90031219955</v>
+      </c>
+      <c r="W71" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>907</v>
       </c>
@@ -5617,8 +6037,14 @@
       <c r="U72" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V72" s="1">
+        <v>311121.2</v>
+      </c>
+      <c r="W72" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>908</v>
       </c>
@@ -5682,8 +6108,14 @@
       <c r="U73" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V73" s="1">
+        <v>307727.76</v>
+      </c>
+      <c r="W73" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1001</v>
       </c>
@@ -5747,8 +6179,14 @@
       <c r="U74" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V74" s="1">
+        <v>320387.5</v>
+      </c>
+      <c r="W74" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1002</v>
       </c>
@@ -5812,8 +6250,14 @@
       <c r="U75" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V75" s="1">
+        <v>274525</v>
+      </c>
+      <c r="W75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1003</v>
       </c>
@@ -5877,8 +6321,14 @@
       <c r="U76" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V76" s="1">
+        <v>360355.93</v>
+      </c>
+      <c r="W76" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1004</v>
       </c>
@@ -5942,8 +6392,14 @@
       <c r="U77" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V77" s="1">
+        <v>310493</v>
+      </c>
+      <c r="W77" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1005</v>
       </c>
@@ -6007,8 +6463,14 @@
       <c r="U78" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V78" s="1">
+        <v>347641.85</v>
+      </c>
+      <c r="W78" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1006</v>
       </c>
@@ -6072,8 +6534,14 @@
       <c r="U79" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V79" s="1">
+        <v>398515.33201774483</v>
+      </c>
+      <c r="W79" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1007</v>
       </c>
@@ -6137,8 +6605,14 @@
       <c r="U80" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V80" s="1">
+        <v>360000</v>
+      </c>
+      <c r="W80" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1008</v>
       </c>
@@ -6202,8 +6676,14 @@
       <c r="U81" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V81" s="1">
+        <v>372544.85473240277</v>
+      </c>
+      <c r="W81" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1101</v>
       </c>
@@ -6267,8 +6747,14 @@
       <c r="U82" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V82" s="1">
+        <v>274525</v>
+      </c>
+      <c r="W82" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1102</v>
       </c>
@@ -6332,8 +6818,14 @@
       <c r="U83" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V83" s="1">
+        <v>338400</v>
+      </c>
+      <c r="W83" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1103</v>
       </c>
@@ -6397,8 +6889,14 @@
       <c r="U84" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V84" s="1">
+        <v>410412.62548237591</v>
+      </c>
+      <c r="W84" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1104</v>
       </c>
@@ -6462,8 +6960,14 @@
       <c r="U85" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V85" s="1">
+        <v>373174.40018964838</v>
+      </c>
+      <c r="W85" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1105</v>
       </c>
@@ -6527,8 +7031,14 @@
       <c r="U86" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V86" s="1">
+        <v>399434.88083385822</v>
+      </c>
+      <c r="W86" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1106</v>
       </c>
@@ -6592,8 +7102,14 @@
       <c r="U87" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V87" s="1">
+        <v>399188.76372328994</v>
+      </c>
+      <c r="W87" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1107</v>
       </c>
@@ -6657,8 +7173,14 @@
       <c r="U88" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V88" s="1">
+        <v>357200</v>
+      </c>
+      <c r="W88" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>1108</v>
       </c>
@@ -6722,8 +7244,14 @@
       <c r="U89" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V89" s="1">
+        <v>399188.76372328994</v>
+      </c>
+      <c r="W89" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>1201</v>
       </c>
@@ -6787,8 +7315,14 @@
       <c r="U90" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V90" s="1">
+        <v>358027</v>
+      </c>
+      <c r="W90" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>1202</v>
       </c>
@@ -6852,8 +7386,14 @@
       <c r="U91" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V91" s="1">
+        <v>338400</v>
+      </c>
+      <c r="W91" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1203</v>
       </c>
@@ -6917,8 +7457,14 @@
       <c r="U92" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V92" s="1">
+        <v>410861.57995273953</v>
+      </c>
+      <c r="W92" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1204</v>
       </c>
@@ -6982,8 +7528,14 @@
       <c r="U93" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V93" s="1">
+        <v>312445.5</v>
+      </c>
+      <c r="W93" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>1205</v>
       </c>
@@ -7047,8 +7599,14 @@
       <c r="U94" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V94" s="1">
+        <v>381988.0365910877</v>
+      </c>
+      <c r="W94" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>1206</v>
       </c>
@@ -7112,8 +7670,14 @@
       <c r="U95" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V95" s="1">
+        <v>312445.5</v>
+      </c>
+      <c r="W95" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>1207</v>
       </c>
@@ -7177,8 +7741,14 @@
       <c r="U96" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V96" s="1">
+        <v>336490</v>
+      </c>
+      <c r="W96" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>1208</v>
       </c>
@@ -7242,8 +7812,14 @@
       <c r="U97" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V97" s="1">
+        <v>370596.7</v>
+      </c>
+      <c r="W97" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1301</v>
       </c>
@@ -7307,8 +7883,14 @@
       <c r="U98" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V98" s="1">
+        <v>264000</v>
+      </c>
+      <c r="W98" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>1302</v>
       </c>
@@ -7372,8 +7954,14 @@
       <c r="U99" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V99" s="1">
+        <v>296695.15000000002</v>
+      </c>
+      <c r="W99" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>1303</v>
       </c>
@@ -7437,8 +8025,14 @@
       <c r="U100" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V100" s="1">
+        <v>411310.53442310274</v>
+      </c>
+      <c r="W100" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>1304</v>
       </c>
@@ -7502,8 +8096,14 @@
       <c r="U101" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V101" s="1">
+        <v>311806.5</v>
+      </c>
+      <c r="W101" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>1305</v>
       </c>
@@ -7567,8 +8167,14 @@
       <c r="U102" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V102" s="1">
+        <v>409065.76207128563</v>
+      </c>
+      <c r="W102" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>1306</v>
       </c>
@@ -7632,8 +8238,14 @@
       <c r="U103" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V103" s="1">
+        <v>329270</v>
+      </c>
+      <c r="W103" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>1307</v>
       </c>
@@ -7697,8 +8309,14 @@
       <c r="U104" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V104" s="1">
+        <v>357200</v>
+      </c>
+      <c r="W104" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>1308</v>
       </c>
@@ -7762,8 +8380,14 @@
       <c r="U105" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V105" s="1">
+        <v>312806.5</v>
+      </c>
+      <c r="W105" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>1401</v>
       </c>
@@ -7827,8 +8451,14 @@
       <c r="U106" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V106" s="1">
+        <v>264000</v>
+      </c>
+      <c r="W106" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>1402</v>
       </c>
@@ -7892,8 +8522,14 @@
       <c r="U107" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V107" s="1">
+        <v>370782.5</v>
+      </c>
+      <c r="W107" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>1403</v>
       </c>
@@ -7957,8 +8593,14 @@
       <c r="U108" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V108" s="1">
+        <v>411759.4888934663</v>
+      </c>
+      <c r="W108" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>1404</v>
       </c>
@@ -8022,8 +8664,14 @@
       <c r="U109" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V109" s="1">
+        <v>400535.62713438016</v>
+      </c>
+      <c r="W109" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>1405</v>
       </c>
@@ -8087,8 +8735,14 @@
       <c r="U110" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V110" s="1">
+        <v>409514.71654164908</v>
+      </c>
+      <c r="W110" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>1406</v>
       </c>
@@ -8152,8 +8806,14 @@
       <c r="U111" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V111" s="1">
+        <v>322710</v>
+      </c>
+      <c r="W111" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>1407</v>
       </c>
@@ -8217,8 +8877,14 @@
       <c r="U112" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V112" s="1">
+        <v>336688.35</v>
+      </c>
+      <c r="W112" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>1408</v>
       </c>
@@ -8282,8 +8948,14 @@
       <c r="U113" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V113" s="1">
+        <v>400535.62713438016</v>
+      </c>
+      <c r="W113" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>1501</v>
       </c>
@@ -8347,8 +9019,14 @@
       <c r="U114" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V114" s="1">
+        <v>330407</v>
+      </c>
+      <c r="W114" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>1502</v>
       </c>
@@ -8412,8 +9090,14 @@
       <c r="U115" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V115" s="1">
+        <v>370000</v>
+      </c>
+      <c r="W115" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>1503</v>
       </c>
@@ -8477,8 +9161,14 @@
       <c r="U116" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V116" s="1">
+        <v>318801.02</v>
+      </c>
+      <c r="W116" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>1504</v>
       </c>
@@ -8542,8 +9232,14 @@
       <c r="U117" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V117" s="1">
+        <v>404542.73719803535</v>
+      </c>
+      <c r="W117" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>1505</v>
       </c>
@@ -8607,8 +9303,14 @@
       <c r="U118" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V118" s="1">
+        <v>319060.34000000003</v>
+      </c>
+      <c r="W118" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>1506</v>
       </c>
@@ -8672,8 +9374,14 @@
       <c r="U119" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V119" s="1">
+        <v>313528.5</v>
+      </c>
+      <c r="W119" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>1507</v>
       </c>
@@ -8737,8 +9445,14 @@
       <c r="U120" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V120" s="1">
+        <v>319060.34999999998</v>
+      </c>
+      <c r="W120" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>1508</v>
       </c>
@@ -8800,6 +9514,12 @@
         <v>347800</v>
       </c>
       <c r="U121" t="s">
+        <v>1</v>
+      </c>
+      <c r="V121" s="1">
+        <v>348166.12</v>
+      </c>
+      <c r="W121" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/vendas-espelho.xlsx
+++ b/data/vendas-espelho.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30030"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE28839-4066-4820-8378-47397387B5F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503CBC0B-D31A-4F7F-B601-5188D053BA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="91">
   <si>
     <t>Und</t>
   </si>
@@ -672,9 +672,9 @@
     <col min="19" max="19" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -1073,6 +1073,12 @@
       <c r="W2" t="s">
         <v>1</v>
       </c>
+      <c r="X2" s="1">
+        <v>330315.8</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -1144,6 +1150,12 @@
       <c r="W3" t="s">
         <v>1</v>
       </c>
+      <c r="X3" s="1">
+        <v>297369</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -1215,6 +1227,12 @@
       <c r="W4" t="s">
         <v>2</v>
       </c>
+      <c r="X4" s="1">
+        <v>390582.10689519066</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -1286,6 +1304,12 @@
       <c r="W5" t="s">
         <v>2</v>
       </c>
+      <c r="X5" s="1">
+        <v>390582.10689519066</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -1357,6 +1381,12 @@
       <c r="W6" t="s">
         <v>2</v>
       </c>
+      <c r="X6" s="1">
+        <v>384822.2206716598</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -1428,6 +1458,12 @@
       <c r="W7" t="s">
         <v>2</v>
       </c>
+      <c r="X7" s="1">
+        <v>390582.10689519066</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -1499,6 +1535,12 @@
       <c r="W8" t="s">
         <v>2</v>
       </c>
+      <c r="X8" s="1">
+        <v>384822.2206716598</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -1570,6 +1612,12 @@
       <c r="W9" t="s">
         <v>1</v>
       </c>
+      <c r="X9" s="1">
+        <v>337748.12</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -1641,6 +1689,12 @@
       <c r="W10" t="s">
         <v>1</v>
       </c>
+      <c r="X10" s="1">
+        <v>351814.23</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -1712,6 +1766,12 @@
       <c r="W11" t="s">
         <v>1</v>
       </c>
+      <c r="X11" s="1">
+        <v>297440.3</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -1783,6 +1843,12 @@
       <c r="W12" t="s">
         <v>1</v>
       </c>
+      <c r="X12" s="1">
+        <v>331760.92</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A13">
@@ -1854,6 +1920,12 @@
       <c r="W13" t="s">
         <v>1</v>
       </c>
+      <c r="X13" s="1">
+        <v>331038.36</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -1925,6 +1997,12 @@
       <c r="W14" t="s">
         <v>1</v>
       </c>
+      <c r="X14" s="1">
+        <v>297708.18</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -1996,6 +2074,12 @@
       <c r="W15" t="s">
         <v>1</v>
       </c>
+      <c r="X15" s="1">
+        <v>312549.92</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -2067,8 +2151,14 @@
       <c r="W16" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X16" s="1">
+        <v>301440</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>208</v>
       </c>
@@ -2138,8 +2228,14 @@
       <c r="W17" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X17" s="1">
+        <v>298038.75</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>301</v>
       </c>
@@ -2209,8 +2305,14 @@
       <c r="W18" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X18" s="1">
+        <v>376741.82444737392</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>302</v>
       </c>
@@ -2280,8 +2382,14 @@
       <c r="W19" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X19" s="1">
+        <v>332171.26</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>303</v>
       </c>
@@ -2351,8 +2459,14 @@
       <c r="W20" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X20" s="1">
+        <v>332171.26</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>304</v>
       </c>
@@ -2422,8 +2536,14 @@
       <c r="W21" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X21" s="1">
+        <v>366249.40015994618</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>305</v>
       </c>
@@ -2493,8 +2613,14 @@
       <c r="W22" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X22" s="1">
+        <v>330268.78999999998</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>306</v>
       </c>
@@ -2564,8 +2690,14 @@
       <c r="W23" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X23" s="1">
+        <v>366249.40015994618</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>307</v>
       </c>
@@ -2635,8 +2767,14 @@
       <c r="W24" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X24" s="1">
+        <v>312960</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>308</v>
       </c>
@@ -2706,8 +2844,14 @@
       <c r="W25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X25" s="1">
+        <v>302905.59999999998</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>401</v>
       </c>
@@ -2777,8 +2921,14 @@
       <c r="W26" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X26" s="1">
+        <v>340000</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>402</v>
       </c>
@@ -2848,8 +2998,14 @@
       <c r="W27" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X27" s="1">
+        <v>377161.52141887089</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>403</v>
       </c>
@@ -2919,8 +3075,14 @@
       <c r="W28" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X28" s="1">
+        <v>325123.86</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>404</v>
       </c>
@@ -2990,8 +3152,14 @@
       <c r="W29" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X29" s="1">
+        <v>396280.28959710058</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>405</v>
       </c>
@@ -3061,8 +3229,14 @@
       <c r="W30" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X30" s="1">
+        <v>375063.03656138532</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>406</v>
       </c>
@@ -3132,8 +3306,14 @@
       <c r="W31" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X31" s="1">
+        <v>392229.96943265648</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>407</v>
       </c>
@@ -3203,8 +3383,14 @@
       <c r="W32" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X32" s="1">
+        <v>323268</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>408</v>
       </c>
@@ -3274,8 +3460,14 @@
       <c r="W33" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X33" s="1">
+        <v>303262.8</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>501</v>
       </c>
@@ -3345,8 +3537,14 @@
       <c r="W34" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X34" s="1">
+        <v>329000</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>502</v>
       </c>
@@ -3416,8 +3614,14 @@
       <c r="W35" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X35" s="1">
+        <v>325500</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>503</v>
       </c>
@@ -3487,8 +3691,14 @@
       <c r="W36" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X36" s="1">
+        <v>377581.21839036816</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>504</v>
       </c>
@@ -3558,8 +3768,14 @@
       <c r="W37" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X37" s="1">
+        <v>303620</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>505</v>
       </c>
@@ -3629,8 +3845,14 @@
       <c r="W38" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X38" s="1">
+        <v>310764</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>506</v>
       </c>
@@ -3700,8 +3922,14 @@
       <c r="W39" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X39" s="1">
+        <v>323419.90000000002</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>507</v>
       </c>
@@ -3771,8 +3999,14 @@
       <c r="W40" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X40" s="1">
+        <v>309763.71999999997</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>508</v>
       </c>
@@ -3842,8 +4076,14 @@
       <c r="W41" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X41" s="1">
+        <v>303620</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>601</v>
       </c>
@@ -3913,8 +4153,14 @@
       <c r="W42" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X42" s="1">
+        <v>311260.31</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>602</v>
       </c>
@@ -3984,8 +4230,14 @@
       <c r="W43" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X43" s="1">
+        <v>312906.25</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>603</v>
       </c>
@@ -4055,8 +4307,14 @@
       <c r="W44" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X44" s="1">
+        <v>312907.2</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>604</v>
       </c>
@@ -4126,8 +4384,14 @@
       <c r="W45" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X45" s="1">
+        <v>302977.2</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>605</v>
       </c>
@@ -4197,8 +4461,14 @@
       <c r="W46" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X46" s="1">
+        <v>402106.96778065222</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>606</v>
       </c>
@@ -4268,8 +4538,14 @@
       <c r="W47" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X47" s="1">
+        <v>323380</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>607</v>
       </c>
@@ -4339,8 +4615,14 @@
       <c r="W48" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X48" s="1">
+        <v>311121.2</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>608</v>
       </c>
@@ -4410,8 +4692,14 @@
       <c r="W49" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X49" s="1">
+        <v>367508.49107443745</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>701</v>
       </c>
@@ -4481,8 +4769,14 @@
       <c r="W50" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X50" s="1">
+        <v>311615.64</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>702</v>
       </c>
@@ -4552,8 +4846,14 @@
       <c r="W51" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X51" s="1">
+        <v>404800.69460283295</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>703</v>
       </c>
@@ -4623,8 +4923,14 @@
       <c r="W52" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X52" s="1">
+        <v>311615.64</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>704</v>
       </c>
@@ -4694,8 +5000,14 @@
       <c r="W53" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X53" s="1">
+        <v>393576.83284374687</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>705</v>
       </c>
@@ -4765,8 +5077,14 @@
       <c r="W54" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X54" s="1">
+        <v>312314.15999999997</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>706</v>
       </c>
@@ -4836,8 +5154,14 @@
       <c r="W55" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X55" s="1">
+        <v>393576.83284374687</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>707</v>
       </c>
@@ -4907,8 +5231,14 @@
       <c r="W56" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X56" s="1">
+        <v>376322.12747587671</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>708</v>
       </c>
@@ -4978,8 +5308,14 @@
       <c r="W57" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X57" s="1">
+        <v>303570.15000000002</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>801</v>
       </c>
@@ -5049,8 +5385,14 @@
       <c r="W58" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X58" s="1">
+        <v>311970.98</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>802</v>
       </c>
@@ -5120,8 +5462,14 @@
       <c r="W59" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X59" s="1">
+        <v>405249.64907319646</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>803</v>
       </c>
@@ -5191,8 +5539,14 @@
       <c r="W60" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X60" s="1">
+        <v>312621.65000000002</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>804</v>
       </c>
@@ -5262,8 +5616,14 @@
       <c r="W61" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X61" s="1">
+        <v>368347.88501743157</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>805</v>
       </c>
@@ -5333,8 +5693,14 @@
       <c r="W62" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X62" s="1">
+        <v>311835.59999999998</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>806</v>
       </c>
@@ -5404,8 +5770,14 @@
       <c r="W63" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X63" s="1">
+        <v>368347.88501743157</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>807</v>
       </c>
@@ -5475,8 +5847,14 @@
       <c r="W64" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X64" s="1">
+        <v>332171.27</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>808</v>
       </c>
@@ -5546,8 +5924,14 @@
       <c r="W65" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X65" s="1">
+        <v>304691.59999999998</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>901</v>
       </c>
@@ -5617,8 +6001,14 @@
       <c r="W66" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X66" s="1">
+        <v>382407.73356258462</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>902</v>
       </c>
@@ -5688,8 +6078,14 @@
       <c r="W67" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X67" s="1">
+        <v>290000</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>903</v>
       </c>
@@ -5759,8 +6155,14 @@
       <c r="W68" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X68" s="1">
+        <v>338158.2</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>904</v>
       </c>
@@ -5830,8 +6232,14 @@
       <c r="W69" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X69" s="1">
+        <v>371915.30927515705</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>905</v>
       </c>
@@ -5901,8 +6309,14 @@
       <c r="W70" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X70" s="1">
+        <v>406820.98971946858</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>906</v>
       </c>
@@ -5972,8 +6386,14 @@
       <c r="W71" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X71" s="1">
+        <v>397841.90031219955</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>907</v>
       </c>
@@ -6043,8 +6463,14 @@
       <c r="W72" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X72" s="1">
+        <v>311121.2</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>908</v>
       </c>
@@ -6114,8 +6540,14 @@
       <c r="W73" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X73" s="1">
+        <v>307727.76</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1001</v>
       </c>
@@ -6185,8 +6617,14 @@
       <c r="W74" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X74" s="1">
+        <v>320387.5</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1002</v>
       </c>
@@ -6256,8 +6694,14 @@
       <c r="W75" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X75" s="1">
+        <v>274525</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1003</v>
       </c>
@@ -6327,8 +6771,14 @@
       <c r="W76" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X76" s="1">
+        <v>360355.93</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1004</v>
       </c>
@@ -6398,8 +6848,14 @@
       <c r="W77" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X77" s="1">
+        <v>310493</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1005</v>
       </c>
@@ -6469,8 +6925,14 @@
       <c r="W78" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X78" s="1">
+        <v>347641.85</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1006</v>
       </c>
@@ -6540,8 +7002,14 @@
       <c r="W79" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X79" s="1">
+        <v>398515.33201774483</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1007</v>
       </c>
@@ -6611,8 +7079,14 @@
       <c r="W80" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X80" s="1">
+        <v>360000</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1008</v>
       </c>
@@ -6682,8 +7156,14 @@
       <c r="W81" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X81" s="1">
+        <v>372544.85473240277</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1101</v>
       </c>
@@ -6753,8 +7233,14 @@
       <c r="W82" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X82" s="1">
+        <v>274525</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1102</v>
       </c>
@@ -6824,8 +7310,14 @@
       <c r="W83" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X83" s="1">
+        <v>338400</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1103</v>
       </c>
@@ -6895,8 +7387,14 @@
       <c r="W84" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X84" s="1">
+        <v>410412.62548237591</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1104</v>
       </c>
@@ -6966,8 +7464,14 @@
       <c r="W85" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X85" s="1">
+        <v>373174.40018964838</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1105</v>
       </c>
@@ -7037,8 +7541,14 @@
       <c r="W86" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X86" s="1">
+        <v>399434.88083385822</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1106</v>
       </c>
@@ -7108,8 +7618,14 @@
       <c r="W87" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X87" s="1">
+        <v>399188.76372328994</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1107</v>
       </c>
@@ -7179,8 +7695,14 @@
       <c r="W88" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X88" s="1">
+        <v>357200</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>1108</v>
       </c>
@@ -7250,8 +7772,14 @@
       <c r="W89" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X89" s="1">
+        <v>370120</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>1201</v>
       </c>
@@ -7321,8 +7849,14 @@
       <c r="W90" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X90" s="1">
+        <v>358027</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>1202</v>
       </c>
@@ -7392,8 +7926,14 @@
       <c r="W91" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X91" s="1">
+        <v>338400</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1203</v>
       </c>
@@ -7463,8 +8003,14 @@
       <c r="W92" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X92" s="1">
+        <v>410861.57995273953</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1204</v>
       </c>
@@ -7534,8 +8080,14 @@
       <c r="W93" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X93" s="1">
+        <v>312445.5</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>1205</v>
       </c>
@@ -7605,8 +8157,14 @@
       <c r="W94" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X94" s="1">
+        <v>381988.0365910877</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>1206</v>
       </c>
@@ -7676,8 +8234,14 @@
       <c r="W95" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X95" s="1">
+        <v>312445.5</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>1207</v>
       </c>
@@ -7747,8 +8311,14 @@
       <c r="W96" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X96" s="1">
+        <v>336490</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>1208</v>
       </c>
@@ -7818,8 +8388,14 @@
       <c r="W97" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X97" s="1">
+        <v>370596.7</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1301</v>
       </c>
@@ -7889,8 +8465,14 @@
       <c r="W98" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X98" s="1">
+        <v>264000</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>1302</v>
       </c>
@@ -7960,8 +8542,14 @@
       <c r="W99" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X99" s="1">
+        <v>296695.15000000002</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>1303</v>
       </c>
@@ -8031,8 +8619,14 @@
       <c r="W100" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X100" s="1">
+        <v>411310.53442310274</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>1304</v>
       </c>
@@ -8102,8 +8696,14 @@
       <c r="W101" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X101" s="1">
+        <v>311806.5</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>1305</v>
       </c>
@@ -8173,8 +8773,14 @@
       <c r="W102" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X102" s="1">
+        <v>409065.76207128563</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>1306</v>
       </c>
@@ -8244,8 +8850,14 @@
       <c r="W103" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X103" s="1">
+        <v>329270</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>1307</v>
       </c>
@@ -8315,8 +8927,14 @@
       <c r="W104" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X104" s="1">
+        <v>357200</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>1308</v>
       </c>
@@ -8386,8 +9004,14 @@
       <c r="W105" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X105" s="1">
+        <v>312806.5</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>1401</v>
       </c>
@@ -8457,8 +9081,14 @@
       <c r="W106" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X106" s="1">
+        <v>264000</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>1402</v>
       </c>
@@ -8528,8 +9158,14 @@
       <c r="W107" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X107" s="1">
+        <v>370782.5</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>1403</v>
       </c>
@@ -8599,8 +9235,14 @@
       <c r="W108" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X108" s="1">
+        <v>411759.4888934663</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>1404</v>
       </c>
@@ -8670,8 +9312,14 @@
       <c r="W109" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X109" s="1">
+        <v>400535.62713438016</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>1405</v>
       </c>
@@ -8741,8 +9389,14 @@
       <c r="W110" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X110" s="1">
+        <v>409514.71654164908</v>
+      </c>
+      <c r="Y110" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>1406</v>
       </c>
@@ -8812,8 +9466,14 @@
       <c r="W111" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X111" s="1">
+        <v>322710</v>
+      </c>
+      <c r="Y111" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>1407</v>
       </c>
@@ -8883,8 +9543,14 @@
       <c r="W112" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X112" s="1">
+        <v>336688.35</v>
+      </c>
+      <c r="Y112" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>1408</v>
       </c>
@@ -8954,8 +9620,14 @@
       <c r="W113" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X113" s="1">
+        <v>370550</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>1501</v>
       </c>
@@ -9025,8 +9697,14 @@
       <c r="W114" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X114" s="1">
+        <v>330407</v>
+      </c>
+      <c r="Y114" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>1502</v>
       </c>
@@ -9096,8 +9774,14 @@
       <c r="W115" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X115" s="1">
+        <v>370000</v>
+      </c>
+      <c r="Y115" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>1503</v>
       </c>
@@ -9167,8 +9851,14 @@
       <c r="W116" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X116" s="1">
+        <v>318801.02</v>
+      </c>
+      <c r="Y116" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>1504</v>
       </c>
@@ -9238,8 +9928,14 @@
       <c r="W117" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X117" s="1">
+        <v>404542.73719803535</v>
+      </c>
+      <c r="Y117" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>1505</v>
       </c>
@@ -9309,8 +10005,14 @@
       <c r="W118" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X118" s="1">
+        <v>319060.34000000003</v>
+      </c>
+      <c r="Y118" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>1506</v>
       </c>
@@ -9380,8 +10082,14 @@
       <c r="W119" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X119" s="1">
+        <v>313528.5</v>
+      </c>
+      <c r="Y119" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>1507</v>
       </c>
@@ -9451,8 +10159,14 @@
       <c r="W120" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X120" s="1">
+        <v>319060.34999999998</v>
+      </c>
+      <c r="Y120" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>1508</v>
       </c>
@@ -9520,6 +10234,12 @@
         <v>348166.12</v>
       </c>
       <c r="W121" t="s">
+        <v>1</v>
+      </c>
+      <c r="X121" s="1">
+        <v>348166.12</v>
+      </c>
+      <c r="Y121" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/vendas-espelho.xlsx
+++ b/data/vendas-espelho.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503CBC0B-D31A-4F7F-B601-5188D053BA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{690F104A-43A5-4D6B-8ED6-1EEFB003C458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="91">
   <si>
     <t>Und</t>
   </si>
@@ -676,8 +676,8 @@
     <col min="23" max="23" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -1079,6 +1079,12 @@
       <c r="Y2" t="s">
         <v>1</v>
       </c>
+      <c r="Z2" s="1">
+        <v>330315.8</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -1156,6 +1162,12 @@
       <c r="Y3" t="s">
         <v>1</v>
       </c>
+      <c r="Z3" s="1">
+        <v>297369</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -1233,6 +1245,12 @@
       <c r="Y4" t="s">
         <v>2</v>
       </c>
+      <c r="Z4" s="1">
+        <v>390582.10689519066</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -1310,6 +1328,12 @@
       <c r="Y5" t="s">
         <v>2</v>
       </c>
+      <c r="Z5" s="1">
+        <v>390582.10689519066</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -1387,6 +1411,12 @@
       <c r="Y6" t="s">
         <v>2</v>
       </c>
+      <c r="Z6" s="1">
+        <v>384822.2206716598</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -1464,6 +1494,12 @@
       <c r="Y7" t="s">
         <v>2</v>
       </c>
+      <c r="Z7" s="1">
+        <v>390582.10689519066</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -1541,6 +1577,12 @@
       <c r="Y8" t="s">
         <v>2</v>
       </c>
+      <c r="Z8" s="1">
+        <v>384822.2206716598</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -1618,6 +1660,12 @@
       <c r="Y9" t="s">
         <v>1</v>
       </c>
+      <c r="Z9" s="1">
+        <v>337748.12</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -1695,6 +1743,12 @@
       <c r="Y10" t="s">
         <v>1</v>
       </c>
+      <c r="Z10" s="1">
+        <v>351814.23</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -1772,6 +1826,12 @@
       <c r="Y11" t="s">
         <v>1</v>
       </c>
+      <c r="Z11" s="1">
+        <v>297440.3</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -1849,6 +1909,12 @@
       <c r="Y12" t="s">
         <v>1</v>
       </c>
+      <c r="Z12" s="1">
+        <v>331760.92</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A13">
@@ -1926,6 +1992,12 @@
       <c r="Y13" t="s">
         <v>1</v>
       </c>
+      <c r="Z13" s="1">
+        <v>331038.36</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -2003,6 +2075,12 @@
       <c r="Y14" t="s">
         <v>1</v>
       </c>
+      <c r="Z14" s="1">
+        <v>297708.18</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -2080,6 +2158,12 @@
       <c r="Y15" t="s">
         <v>1</v>
       </c>
+      <c r="Z15" s="1">
+        <v>312549.92</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -2157,8 +2241,14 @@
       <c r="Y16" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z16" s="1">
+        <v>301440</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>208</v>
       </c>
@@ -2234,8 +2324,14 @@
       <c r="Y17" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z17" s="1">
+        <v>298038.75</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>301</v>
       </c>
@@ -2311,8 +2407,14 @@
       <c r="Y18" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z18" s="1">
+        <v>376741.82444737392</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>302</v>
       </c>
@@ -2388,8 +2490,14 @@
       <c r="Y19" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z19" s="1">
+        <v>332171.26</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>303</v>
       </c>
@@ -2465,8 +2573,14 @@
       <c r="Y20" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z20" s="1">
+        <v>332171.26</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>304</v>
       </c>
@@ -2542,8 +2656,14 @@
       <c r="Y21" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z21" s="1">
+        <v>366249.40015994618</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>305</v>
       </c>
@@ -2619,8 +2739,14 @@
       <c r="Y22" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z22" s="1">
+        <v>330268.78999999998</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>306</v>
       </c>
@@ -2696,8 +2822,14 @@
       <c r="Y23" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z23" s="1">
+        <v>366249.40015994618</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>307</v>
       </c>
@@ -2773,8 +2905,14 @@
       <c r="Y24" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z24" s="1">
+        <v>312960</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>308</v>
       </c>
@@ -2850,8 +2988,14 @@
       <c r="Y25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z25" s="1">
+        <v>302905.59999999998</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>401</v>
       </c>
@@ -2927,8 +3071,14 @@
       <c r="Y26" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z26" s="1">
+        <v>340000</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>402</v>
       </c>
@@ -3004,8 +3154,14 @@
       <c r="Y27" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z27" s="1">
+        <v>377161.52141887089</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>403</v>
       </c>
@@ -3081,8 +3237,14 @@
       <c r="Y28" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z28" s="1">
+        <v>325123.86</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>404</v>
       </c>
@@ -3158,8 +3320,14 @@
       <c r="Y29" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z29" s="1">
+        <v>396280.28959710058</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>405</v>
       </c>
@@ -3235,8 +3403,14 @@
       <c r="Y30" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z30" s="1">
+        <v>375063.03656138532</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>406</v>
       </c>
@@ -3312,8 +3486,14 @@
       <c r="Y31" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z31" s="1">
+        <v>392229.96943265648</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>407</v>
       </c>
@@ -3389,8 +3569,14 @@
       <c r="Y32" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z32" s="1">
+        <v>323268</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>408</v>
       </c>
@@ -3466,8 +3652,14 @@
       <c r="Y33" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z33" s="1">
+        <v>303262.8</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>501</v>
       </c>
@@ -3543,8 +3735,14 @@
       <c r="Y34" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z34" s="1">
+        <v>329000</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>502</v>
       </c>
@@ -3620,8 +3818,14 @@
       <c r="Y35" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z35" s="1">
+        <v>325500</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>503</v>
       </c>
@@ -3697,8 +3901,14 @@
       <c r="Y36" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z36" s="1">
+        <v>377581.21839036816</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>504</v>
       </c>
@@ -3774,8 +3984,14 @@
       <c r="Y37" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z37" s="1">
+        <v>303620</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>505</v>
       </c>
@@ -3851,8 +4067,14 @@
       <c r="Y38" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z38" s="1">
+        <v>310764</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>506</v>
       </c>
@@ -3928,8 +4150,14 @@
       <c r="Y39" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z39" s="1">
+        <v>323419.90000000002</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>507</v>
       </c>
@@ -4005,8 +4233,14 @@
       <c r="Y40" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z40" s="1">
+        <v>309763.71999999997</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>508</v>
       </c>
@@ -4082,8 +4316,14 @@
       <c r="Y41" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z41" s="1">
+        <v>303620</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>601</v>
       </c>
@@ -4159,8 +4399,14 @@
       <c r="Y42" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z42" s="1">
+        <v>311260.31</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>602</v>
       </c>
@@ -4236,8 +4482,14 @@
       <c r="Y43" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z43" s="1">
+        <v>312906.25</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>603</v>
       </c>
@@ -4313,8 +4565,14 @@
       <c r="Y44" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z44" s="1">
+        <v>312907.2</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>604</v>
       </c>
@@ -4390,8 +4648,14 @@
       <c r="Y45" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z45" s="1">
+        <v>302977.2</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>605</v>
       </c>
@@ -4467,8 +4731,14 @@
       <c r="Y46" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z46" s="1">
+        <v>402106.96778065222</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>606</v>
       </c>
@@ -4544,8 +4814,14 @@
       <c r="Y47" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z47" s="1">
+        <v>323380</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>607</v>
       </c>
@@ -4621,8 +4897,14 @@
       <c r="Y48" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z48" s="1">
+        <v>311121.2</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>608</v>
       </c>
@@ -4698,8 +4980,14 @@
       <c r="Y49" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z49" s="1">
+        <v>367508.49107443745</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>701</v>
       </c>
@@ -4775,8 +5063,14 @@
       <c r="Y50" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z50" s="1">
+        <v>311615.64</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>702</v>
       </c>
@@ -4852,8 +5146,14 @@
       <c r="Y51" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z51" s="1">
+        <v>364345.22</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>703</v>
       </c>
@@ -4929,8 +5229,14 @@
       <c r="Y52" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z52" s="1">
+        <v>311615.64</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>704</v>
       </c>
@@ -5006,8 +5312,14 @@
       <c r="Y53" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z53" s="1">
+        <v>393576.83284374687</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>705</v>
       </c>
@@ -5083,8 +5395,14 @@
       <c r="Y54" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z54" s="1">
+        <v>312314.15999999997</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>706</v>
       </c>
@@ -5160,8 +5478,14 @@
       <c r="Y55" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z55" s="1">
+        <v>393576.83284374687</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>707</v>
       </c>
@@ -5237,8 +5561,14 @@
       <c r="Y56" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z56" s="1">
+        <v>376322.12747587671</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>708</v>
       </c>
@@ -5314,8 +5644,14 @@
       <c r="Y57" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z57" s="1">
+        <v>303570.15000000002</v>
+      </c>
+      <c r="AA57" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>801</v>
       </c>
@@ -5391,8 +5727,14 @@
       <c r="Y58" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z58" s="1">
+        <v>311970.98</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>802</v>
       </c>
@@ -5468,8 +5810,14 @@
       <c r="Y59" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z59" s="1">
+        <v>405249.64907319646</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>803</v>
       </c>
@@ -5545,8 +5893,14 @@
       <c r="Y60" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z60" s="1">
+        <v>312621.65000000002</v>
+      </c>
+      <c r="AA60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>804</v>
       </c>
@@ -5622,8 +5976,14 @@
       <c r="Y61" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z61" s="1">
+        <v>368347.88501743157</v>
+      </c>
+      <c r="AA61" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>805</v>
       </c>
@@ -5699,8 +6059,14 @@
       <c r="Y62" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z62" s="1">
+        <v>311835.59999999998</v>
+      </c>
+      <c r="AA62" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>806</v>
       </c>
@@ -5776,8 +6142,14 @@
       <c r="Y63" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z63" s="1">
+        <v>368347.88501743157</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>807</v>
       </c>
@@ -5853,8 +6225,14 @@
       <c r="Y64" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z64" s="1">
+        <v>332171.27</v>
+      </c>
+      <c r="AA64" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>808</v>
       </c>
@@ -5930,8 +6308,14 @@
       <c r="Y65" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z65" s="1">
+        <v>304691.59999999998</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>901</v>
       </c>
@@ -6007,8 +6391,14 @@
       <c r="Y66" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z66" s="1">
+        <v>382407.73356258462</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>902</v>
       </c>
@@ -6084,8 +6474,14 @@
       <c r="Y67" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z67" s="1">
+        <v>290000</v>
+      </c>
+      <c r="AA67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>903</v>
       </c>
@@ -6161,8 +6557,14 @@
       <c r="Y68" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z68" s="1">
+        <v>338158.2</v>
+      </c>
+      <c r="AA68" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>904</v>
       </c>
@@ -6238,8 +6640,14 @@
       <c r="Y69" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z69" s="1">
+        <v>371915.30927515705</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>905</v>
       </c>
@@ -6315,8 +6723,14 @@
       <c r="Y70" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z70" s="1">
+        <v>406820.98971946858</v>
+      </c>
+      <c r="AA70" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>906</v>
       </c>
@@ -6392,8 +6806,14 @@
       <c r="Y71" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z71" s="1">
+        <v>397841.90031219955</v>
+      </c>
+      <c r="AA71" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>907</v>
       </c>
@@ -6469,8 +6889,14 @@
       <c r="Y72" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z72" s="1">
+        <v>311121.2</v>
+      </c>
+      <c r="AA72" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>908</v>
       </c>
@@ -6546,8 +6972,14 @@
       <c r="Y73" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z73" s="1">
+        <v>307727.76</v>
+      </c>
+      <c r="AA73" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1001</v>
       </c>
@@ -6623,8 +7055,14 @@
       <c r="Y74" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z74" s="1">
+        <v>320387.5</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1002</v>
       </c>
@@ -6700,8 +7138,14 @@
       <c r="Y75" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z75" s="1">
+        <v>274525</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1003</v>
       </c>
@@ -6777,8 +7221,14 @@
       <c r="Y76" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z76" s="1">
+        <v>360355.93</v>
+      </c>
+      <c r="AA76" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1004</v>
       </c>
@@ -6854,8 +7304,14 @@
       <c r="Y77" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z77" s="1">
+        <v>310493</v>
+      </c>
+      <c r="AA77" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1005</v>
       </c>
@@ -6931,8 +7387,14 @@
       <c r="Y78" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z78" s="1">
+        <v>347641.85</v>
+      </c>
+      <c r="AA78" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1006</v>
       </c>
@@ -7008,8 +7470,14 @@
       <c r="Y79" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z79" s="1">
+        <v>398515.33201774483</v>
+      </c>
+      <c r="AA79" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1007</v>
       </c>
@@ -7085,8 +7553,14 @@
       <c r="Y80" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z80" s="1">
+        <v>360000</v>
+      </c>
+      <c r="AA80" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1008</v>
       </c>
@@ -7162,8 +7636,14 @@
       <c r="Y81" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z81" s="1">
+        <v>372544.85473240277</v>
+      </c>
+      <c r="AA81" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1101</v>
       </c>
@@ -7239,8 +7719,14 @@
       <c r="Y82" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z82" s="1">
+        <v>274525</v>
+      </c>
+      <c r="AA82" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1102</v>
       </c>
@@ -7316,8 +7802,14 @@
       <c r="Y83" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z83" s="1">
+        <v>338400</v>
+      </c>
+      <c r="AA83" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1103</v>
       </c>
@@ -7393,8 +7885,14 @@
       <c r="Y84" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z84" s="1">
+        <v>410412.62548237591</v>
+      </c>
+      <c r="AA84" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1104</v>
       </c>
@@ -7470,8 +7968,14 @@
       <c r="Y85" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z85" s="1">
+        <v>373174.40018964838</v>
+      </c>
+      <c r="AA85" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1105</v>
       </c>
@@ -7547,8 +8051,14 @@
       <c r="Y86" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z86" s="1">
+        <v>399434.88083385822</v>
+      </c>
+      <c r="AA86" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1106</v>
       </c>
@@ -7624,8 +8134,14 @@
       <c r="Y87" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z87" s="1">
+        <v>399188.76372328994</v>
+      </c>
+      <c r="AA87" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1107</v>
       </c>
@@ -7701,8 +8217,14 @@
       <c r="Y88" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z88" s="1">
+        <v>357200</v>
+      </c>
+      <c r="AA88" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>1108</v>
       </c>
@@ -7778,8 +8300,14 @@
       <c r="Y89" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z89" s="1">
+        <v>370120</v>
+      </c>
+      <c r="AA89" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>1201</v>
       </c>
@@ -7855,8 +8383,14 @@
       <c r="Y90" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z90" s="1">
+        <v>358027</v>
+      </c>
+      <c r="AA90" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>1202</v>
       </c>
@@ -7932,8 +8466,14 @@
       <c r="Y91" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z91" s="1">
+        <v>338400</v>
+      </c>
+      <c r="AA91" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1203</v>
       </c>
@@ -8009,8 +8549,14 @@
       <c r="Y92" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z92" s="1">
+        <v>410861.57995273953</v>
+      </c>
+      <c r="AA92" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1204</v>
       </c>
@@ -8086,8 +8632,14 @@
       <c r="Y93" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z93" s="1">
+        <v>312445.5</v>
+      </c>
+      <c r="AA93" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>1205</v>
       </c>
@@ -8163,8 +8715,14 @@
       <c r="Y94" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z94" s="1">
+        <v>381988.0365910877</v>
+      </c>
+      <c r="AA94" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>1206</v>
       </c>
@@ -8240,8 +8798,14 @@
       <c r="Y95" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z95" s="1">
+        <v>312445.5</v>
+      </c>
+      <c r="AA95" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>1207</v>
       </c>
@@ -8317,8 +8881,14 @@
       <c r="Y96" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z96" s="1">
+        <v>336490</v>
+      </c>
+      <c r="AA96" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>1208</v>
       </c>
@@ -8394,8 +8964,14 @@
       <c r="Y97" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z97" s="1">
+        <v>370596.7</v>
+      </c>
+      <c r="AA97" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1301</v>
       </c>
@@ -8471,8 +9047,14 @@
       <c r="Y98" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z98" s="1">
+        <v>264000</v>
+      </c>
+      <c r="AA98" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>1302</v>
       </c>
@@ -8548,8 +9130,14 @@
       <c r="Y99" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z99" s="1">
+        <v>296695.15000000002</v>
+      </c>
+      <c r="AA99" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>1303</v>
       </c>
@@ -8625,8 +9213,14 @@
       <c r="Y100" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z100" s="1">
+        <v>411310.53442310274</v>
+      </c>
+      <c r="AA100" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>1304</v>
       </c>
@@ -8702,8 +9296,14 @@
       <c r="Y101" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z101" s="1">
+        <v>311806.5</v>
+      </c>
+      <c r="AA101" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>1305</v>
       </c>
@@ -8779,8 +9379,14 @@
       <c r="Y102" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z102" s="1">
+        <v>409065.76207128563</v>
+      </c>
+      <c r="AA102" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>1306</v>
       </c>
@@ -8856,8 +9462,14 @@
       <c r="Y103" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z103" s="1">
+        <v>329270</v>
+      </c>
+      <c r="AA103" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>1307</v>
       </c>
@@ -8933,8 +9545,14 @@
       <c r="Y104" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z104" s="1">
+        <v>357200</v>
+      </c>
+      <c r="AA104" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>1308</v>
       </c>
@@ -9010,8 +9628,14 @@
       <c r="Y105" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z105" s="1">
+        <v>312806.5</v>
+      </c>
+      <c r="AA105" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>1401</v>
       </c>
@@ -9087,8 +9711,14 @@
       <c r="Y106" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z106" s="1">
+        <v>264000</v>
+      </c>
+      <c r="AA106" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>1402</v>
       </c>
@@ -9164,8 +9794,14 @@
       <c r="Y107" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z107" s="1">
+        <v>370782.5</v>
+      </c>
+      <c r="AA107" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>1403</v>
       </c>
@@ -9241,8 +9877,14 @@
       <c r="Y108" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z108" s="1">
+        <v>411759.4888934663</v>
+      </c>
+      <c r="AA108" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>1404</v>
       </c>
@@ -9318,8 +9960,14 @@
       <c r="Y109" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z109" s="1">
+        <v>400535.62713438016</v>
+      </c>
+      <c r="AA109" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>1405</v>
       </c>
@@ -9395,8 +10043,14 @@
       <c r="Y110" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z110" s="1">
+        <v>409514.71654164908</v>
+      </c>
+      <c r="AA110" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>1406</v>
       </c>
@@ -9472,8 +10126,14 @@
       <c r="Y111" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z111" s="1">
+        <v>322710</v>
+      </c>
+      <c r="AA111" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>1407</v>
       </c>
@@ -9549,8 +10209,14 @@
       <c r="Y112" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z112" s="1">
+        <v>336688.35</v>
+      </c>
+      <c r="AA112" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>1408</v>
       </c>
@@ -9626,8 +10292,14 @@
       <c r="Y113" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z113" s="1">
+        <v>370550</v>
+      </c>
+      <c r="AA113" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>1501</v>
       </c>
@@ -9703,8 +10375,14 @@
       <c r="Y114" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z114" s="1">
+        <v>330407</v>
+      </c>
+      <c r="AA114" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>1502</v>
       </c>
@@ -9780,8 +10458,14 @@
       <c r="Y115" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z115" s="1">
+        <v>370000</v>
+      </c>
+      <c r="AA115" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>1503</v>
       </c>
@@ -9857,8 +10541,14 @@
       <c r="Y116" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z116" s="1">
+        <v>318801.02</v>
+      </c>
+      <c r="AA116" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>1504</v>
       </c>
@@ -9934,8 +10624,14 @@
       <c r="Y117" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z117" s="1">
+        <v>404542.73719803535</v>
+      </c>
+      <c r="AA117" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>1505</v>
       </c>
@@ -10011,8 +10707,14 @@
       <c r="Y118" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z118" s="1">
+        <v>319060.34000000003</v>
+      </c>
+      <c r="AA118" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>1506</v>
       </c>
@@ -10088,8 +10790,14 @@
       <c r="Y119" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z119" s="1">
+        <v>313528.5</v>
+      </c>
+      <c r="AA119" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>1507</v>
       </c>
@@ -10165,8 +10873,14 @@
       <c r="Y120" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z120" s="1">
+        <v>319060.34999999998</v>
+      </c>
+      <c r="AA120" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>1508</v>
       </c>
@@ -10240,6 +10954,12 @@
         <v>348166.12</v>
       </c>
       <c r="Y121" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z121" s="1">
+        <v>348166.12</v>
+      </c>
+      <c r="AA121" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/vendas-espelho.xlsx
+++ b/data/vendas-espelho.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{690F104A-43A5-4D6B-8ED6-1EEFB003C458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1064AAB3-0644-4549-BC9C-578C30321E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="91">
   <si>
     <t>Und</t>
   </si>
@@ -678,7 +678,7 @@
     <col min="25" max="25" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -1085,6 +1085,12 @@
       <c r="AA2" t="s">
         <v>1</v>
       </c>
+      <c r="AB2" s="1">
+        <v>330315.8</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -1168,6 +1174,12 @@
       <c r="AA3" t="s">
         <v>1</v>
       </c>
+      <c r="AB3" s="1">
+        <v>297369</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -1251,6 +1263,12 @@
       <c r="AA4" t="s">
         <v>2</v>
       </c>
+      <c r="AB4" s="1">
+        <v>390582.10689519066</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -1334,6 +1352,12 @@
       <c r="AA5" t="s">
         <v>2</v>
       </c>
+      <c r="AB5" s="1">
+        <v>390582.10689519066</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -1417,6 +1441,12 @@
       <c r="AA6" t="s">
         <v>2</v>
       </c>
+      <c r="AB6" s="1">
+        <v>384822.2206716598</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -1500,6 +1530,12 @@
       <c r="AA7" t="s">
         <v>2</v>
       </c>
+      <c r="AB7" s="1">
+        <v>390582.10689519066</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -1583,6 +1619,12 @@
       <c r="AA8" t="s">
         <v>2</v>
       </c>
+      <c r="AB8" s="1">
+        <v>384822.2206716598</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -1666,6 +1708,12 @@
       <c r="AA9" t="s">
         <v>1</v>
       </c>
+      <c r="AB9" s="1">
+        <v>337748.12</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -1749,6 +1797,12 @@
       <c r="AA10" t="s">
         <v>1</v>
       </c>
+      <c r="AB10" s="1">
+        <v>351814.23</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -1832,6 +1886,12 @@
       <c r="AA11" t="s">
         <v>1</v>
       </c>
+      <c r="AB11" s="1">
+        <v>297440.3</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -1915,6 +1975,12 @@
       <c r="AA12" t="s">
         <v>1</v>
       </c>
+      <c r="AB12" s="1">
+        <v>331760.92</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A13">
@@ -1998,6 +2064,12 @@
       <c r="AA13" t="s">
         <v>1</v>
       </c>
+      <c r="AB13" s="1">
+        <v>331038.36</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -2081,6 +2153,12 @@
       <c r="AA14" t="s">
         <v>1</v>
       </c>
+      <c r="AB14" s="1">
+        <v>297708.18</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -2164,6 +2242,12 @@
       <c r="AA15" t="s">
         <v>1</v>
       </c>
+      <c r="AB15" s="1">
+        <v>312549.92</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -2247,8 +2331,14 @@
       <c r="AA16" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB16" s="1">
+        <v>301440</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>208</v>
       </c>
@@ -2330,8 +2420,14 @@
       <c r="AA17" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB17" s="1">
+        <v>298038.75</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>301</v>
       </c>
@@ -2413,8 +2509,14 @@
       <c r="AA18" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB18" s="1">
+        <v>376741.82444737392</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>302</v>
       </c>
@@ -2496,8 +2598,14 @@
       <c r="AA19" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB19" s="1">
+        <v>332171.26</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>303</v>
       </c>
@@ -2579,8 +2687,14 @@
       <c r="AA20" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB20" s="1">
+        <v>332171.26</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>304</v>
       </c>
@@ -2662,8 +2776,14 @@
       <c r="AA21" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB21" s="1">
+        <v>366249.40015994618</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>305</v>
       </c>
@@ -2745,8 +2865,14 @@
       <c r="AA22" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB22" s="1">
+        <v>330268.78999999998</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>306</v>
       </c>
@@ -2828,8 +2954,14 @@
       <c r="AA23" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB23" s="1">
+        <v>366249.40015994618</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>307</v>
       </c>
@@ -2911,8 +3043,14 @@
       <c r="AA24" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB24" s="1">
+        <v>312960</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>308</v>
       </c>
@@ -2994,8 +3132,14 @@
       <c r="AA25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB25" s="1">
+        <v>302905.59999999998</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>401</v>
       </c>
@@ -3077,8 +3221,14 @@
       <c r="AA26" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB26" s="1">
+        <v>340000</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>402</v>
       </c>
@@ -3160,8 +3310,14 @@
       <c r="AA27" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB27" s="1">
+        <v>377161.52141887089</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>403</v>
       </c>
@@ -3243,8 +3399,14 @@
       <c r="AA28" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB28" s="1">
+        <v>325123.86</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>404</v>
       </c>
@@ -3326,8 +3488,14 @@
       <c r="AA29" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB29" s="1">
+        <v>396280.28959710058</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>405</v>
       </c>
@@ -3409,8 +3577,14 @@
       <c r="AA30" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB30" s="1">
+        <v>375063.03656138532</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>406</v>
       </c>
@@ -3492,8 +3666,14 @@
       <c r="AA31" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB31" s="1">
+        <v>392229.96943265648</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>407</v>
       </c>
@@ -3575,8 +3755,14 @@
       <c r="AA32" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB32" s="1">
+        <v>323268</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>408</v>
       </c>
@@ -3658,8 +3844,14 @@
       <c r="AA33" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB33" s="1">
+        <v>303262.8</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>501</v>
       </c>
@@ -3741,8 +3933,14 @@
       <c r="AA34" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB34" s="1">
+        <v>329000</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>502</v>
       </c>
@@ -3824,8 +4022,14 @@
       <c r="AA35" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB35" s="1">
+        <v>325500</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>503</v>
       </c>
@@ -3907,8 +4111,14 @@
       <c r="AA36" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB36" s="1">
+        <v>377581.21839036816</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>504</v>
       </c>
@@ -3990,8 +4200,14 @@
       <c r="AA37" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB37" s="1">
+        <v>303620</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>505</v>
       </c>
@@ -4073,8 +4289,14 @@
       <c r="AA38" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB38" s="1">
+        <v>310764</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>506</v>
       </c>
@@ -4156,8 +4378,14 @@
       <c r="AA39" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB39" s="1">
+        <v>323419.90000000002</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>507</v>
       </c>
@@ -4239,8 +4467,14 @@
       <c r="AA40" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB40" s="1">
+        <v>309763.71999999997</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>508</v>
       </c>
@@ -4322,8 +4556,14 @@
       <c r="AA41" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB41" s="1">
+        <v>303620</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>601</v>
       </c>
@@ -4405,8 +4645,14 @@
       <c r="AA42" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB42" s="1">
+        <v>311260.31</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>602</v>
       </c>
@@ -4488,8 +4734,14 @@
       <c r="AA43" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB43" s="1">
+        <v>370514.8</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>603</v>
       </c>
@@ -4571,8 +4823,14 @@
       <c r="AA44" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB44" s="1">
+        <v>312907.2</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>604</v>
       </c>
@@ -4654,8 +4912,14 @@
       <c r="AA45" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB45" s="1">
+        <v>302977.2</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>605</v>
       </c>
@@ -4737,8 +5001,14 @@
       <c r="AA46" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB46" s="1">
+        <v>370674.7</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>606</v>
       </c>
@@ -4820,8 +5090,14 @@
       <c r="AA47" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB47" s="1">
+        <v>323380</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>607</v>
       </c>
@@ -4903,8 +5179,14 @@
       <c r="AA48" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB48" s="1">
+        <v>311121.2</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>608</v>
       </c>
@@ -4986,8 +5268,14 @@
       <c r="AA49" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB49" s="1">
+        <v>367508.49107443745</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>701</v>
       </c>
@@ -5069,8 +5357,14 @@
       <c r="AA50" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB50" s="1">
+        <v>311615.64</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>702</v>
       </c>
@@ -5152,8 +5446,14 @@
       <c r="AA51" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB51" s="1">
+        <v>364345.22</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>703</v>
       </c>
@@ -5235,8 +5535,14 @@
       <c r="AA52" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB52" s="1">
+        <v>311615.64</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>704</v>
       </c>
@@ -5318,8 +5624,14 @@
       <c r="AA53" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB53" s="1">
+        <v>393576.83284374687</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>705</v>
       </c>
@@ -5401,8 +5713,14 @@
       <c r="AA54" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB54" s="1">
+        <v>312314.15999999997</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>706</v>
       </c>
@@ -5484,8 +5802,14 @@
       <c r="AA55" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB55" s="1">
+        <v>393576.83284374687</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>707</v>
       </c>
@@ -5567,8 +5891,14 @@
       <c r="AA56" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB56" s="1">
+        <v>376322.12747587671</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>708</v>
       </c>
@@ -5650,8 +5980,14 @@
       <c r="AA57" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB57" s="1">
+        <v>303570.15000000002</v>
+      </c>
+      <c r="AC57" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>801</v>
       </c>
@@ -5733,8 +6069,14 @@
       <c r="AA58" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB58" s="1">
+        <v>311970.98</v>
+      </c>
+      <c r="AC58" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>802</v>
       </c>
@@ -5816,8 +6158,14 @@
       <c r="AA59" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB59" s="1">
+        <v>375540.19</v>
+      </c>
+      <c r="AC59" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>803</v>
       </c>
@@ -5899,8 +6247,14 @@
       <c r="AA60" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB60" s="1">
+        <v>312621.65000000002</v>
+      </c>
+      <c r="AC60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>804</v>
       </c>
@@ -5982,8 +6336,14 @@
       <c r="AA61" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB61" s="1">
+        <v>368347.88501743157</v>
+      </c>
+      <c r="AC61" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="62" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>805</v>
       </c>
@@ -6065,8 +6425,14 @@
       <c r="AA62" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB62" s="1">
+        <v>311835.59999999998</v>
+      </c>
+      <c r="AC62" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>806</v>
       </c>
@@ -6148,8 +6514,14 @@
       <c r="AA63" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB63" s="1">
+        <v>368347.88501743157</v>
+      </c>
+      <c r="AC63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>807</v>
       </c>
@@ -6231,8 +6603,14 @@
       <c r="AA64" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB64" s="1">
+        <v>332171.27</v>
+      </c>
+      <c r="AC64" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>808</v>
       </c>
@@ -6314,8 +6692,14 @@
       <c r="AA65" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB65" s="1">
+        <v>304691.59999999998</v>
+      </c>
+      <c r="AC65" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>901</v>
       </c>
@@ -6397,8 +6781,14 @@
       <c r="AA66" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB66" s="1">
+        <v>382407.73356258462</v>
+      </c>
+      <c r="AC66" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="67" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>902</v>
       </c>
@@ -6480,8 +6870,14 @@
       <c r="AA67" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB67" s="1">
+        <v>290000</v>
+      </c>
+      <c r="AC67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>903</v>
       </c>
@@ -6563,8 +6959,14 @@
       <c r="AA68" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB68" s="1">
+        <v>338158.2</v>
+      </c>
+      <c r="AC68" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>904</v>
       </c>
@@ -6646,8 +7048,14 @@
       <c r="AA69" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB69" s="1">
+        <v>371915.30927515705</v>
+      </c>
+      <c r="AC69" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>905</v>
       </c>
@@ -6729,8 +7137,14 @@
       <c r="AA70" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB70" s="1">
+        <v>406820.98971946858</v>
+      </c>
+      <c r="AC70" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>906</v>
       </c>
@@ -6812,8 +7226,14 @@
       <c r="AA71" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB71" s="1">
+        <v>397841.90031219955</v>
+      </c>
+      <c r="AC71" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>907</v>
       </c>
@@ -6895,8 +7315,14 @@
       <c r="AA72" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB72" s="1">
+        <v>311121.2</v>
+      </c>
+      <c r="AC72" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>908</v>
       </c>
@@ -6978,8 +7404,14 @@
       <c r="AA73" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB73" s="1">
+        <v>307727.76</v>
+      </c>
+      <c r="AC73" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1001</v>
       </c>
@@ -7061,8 +7493,14 @@
       <c r="AA74" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB74" s="1">
+        <v>320387.5</v>
+      </c>
+      <c r="AC74" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1002</v>
       </c>
@@ -7144,8 +7582,14 @@
       <c r="AA75" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB75" s="1">
+        <v>274525</v>
+      </c>
+      <c r="AC75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1003</v>
       </c>
@@ -7227,8 +7671,14 @@
       <c r="AA76" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB76" s="1">
+        <v>360355.93</v>
+      </c>
+      <c r="AC76" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1004</v>
       </c>
@@ -7310,8 +7760,14 @@
       <c r="AA77" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB77" s="1">
+        <v>310493</v>
+      </c>
+      <c r="AC77" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1005</v>
       </c>
@@ -7393,8 +7849,14 @@
       <c r="AA78" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB78" s="1">
+        <v>347641.85</v>
+      </c>
+      <c r="AC78" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1006</v>
       </c>
@@ -7476,8 +7938,14 @@
       <c r="AA79" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB79" s="1">
+        <v>398515.33201774483</v>
+      </c>
+      <c r="AC79" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1007</v>
       </c>
@@ -7559,8 +8027,14 @@
       <c r="AA80" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB80" s="1">
+        <v>360000</v>
+      </c>
+      <c r="AC80" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1008</v>
       </c>
@@ -7642,8 +8116,14 @@
       <c r="AA81" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB81" s="1">
+        <v>372544.85473240277</v>
+      </c>
+      <c r="AC81" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="82" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1101</v>
       </c>
@@ -7725,8 +8205,14 @@
       <c r="AA82" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB82" s="1">
+        <v>274525</v>
+      </c>
+      <c r="AC82" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1102</v>
       </c>
@@ -7808,8 +8294,14 @@
       <c r="AA83" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB83" s="1">
+        <v>338400</v>
+      </c>
+      <c r="AC83" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1103</v>
       </c>
@@ -7891,8 +8383,14 @@
       <c r="AA84" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB84" s="1">
+        <v>410412.62548237591</v>
+      </c>
+      <c r="AC84" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1104</v>
       </c>
@@ -7974,8 +8472,14 @@
       <c r="AA85" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB85" s="1">
+        <v>373174.40018964838</v>
+      </c>
+      <c r="AC85" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="86" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1105</v>
       </c>
@@ -8057,8 +8561,14 @@
       <c r="AA86" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB86" s="1">
+        <v>399434.88083385822</v>
+      </c>
+      <c r="AC86" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1106</v>
       </c>
@@ -8140,8 +8650,14 @@
       <c r="AA87" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB87" s="1">
+        <v>399188.76372328994</v>
+      </c>
+      <c r="AC87" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1107</v>
       </c>
@@ -8223,8 +8739,14 @@
       <c r="AA88" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB88" s="1">
+        <v>357200</v>
+      </c>
+      <c r="AC88" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>1108</v>
       </c>
@@ -8306,8 +8828,14 @@
       <c r="AA89" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB89" s="1">
+        <v>370120</v>
+      </c>
+      <c r="AC89" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>1201</v>
       </c>
@@ -8389,8 +8917,14 @@
       <c r="AA90" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB90" s="1">
+        <v>358027</v>
+      </c>
+      <c r="AC90" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>1202</v>
       </c>
@@ -8472,8 +9006,14 @@
       <c r="AA91" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB91" s="1">
+        <v>338400</v>
+      </c>
+      <c r="AC91" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1203</v>
       </c>
@@ -8555,8 +9095,14 @@
       <c r="AA92" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB92" s="1">
+        <v>410861.57995273953</v>
+      </c>
+      <c r="AC92" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1204</v>
       </c>
@@ -8638,8 +9184,14 @@
       <c r="AA93" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB93" s="1">
+        <v>312445.5</v>
+      </c>
+      <c r="AC93" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>1205</v>
       </c>
@@ -8721,8 +9273,14 @@
       <c r="AA94" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB94" s="1">
+        <v>381988.0365910877</v>
+      </c>
+      <c r="AC94" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="95" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>1206</v>
       </c>
@@ -8804,8 +9362,14 @@
       <c r="AA95" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB95" s="1">
+        <v>312445.5</v>
+      </c>
+      <c r="AC95" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>1207</v>
       </c>
@@ -8887,8 +9451,14 @@
       <c r="AA96" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB96" s="1">
+        <v>336490</v>
+      </c>
+      <c r="AC96" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>1208</v>
       </c>
@@ -8970,8 +9540,14 @@
       <c r="AA97" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB97" s="1">
+        <v>370596.7</v>
+      </c>
+      <c r="AC97" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1301</v>
       </c>
@@ -9053,8 +9629,14 @@
       <c r="AA98" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB98" s="1">
+        <v>264000</v>
+      </c>
+      <c r="AC98" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>1302</v>
       </c>
@@ -9136,8 +9718,14 @@
       <c r="AA99" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB99" s="1">
+        <v>296695.15000000002</v>
+      </c>
+      <c r="AC99" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>1303</v>
       </c>
@@ -9219,8 +9807,14 @@
       <c r="AA100" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB100" s="1">
+        <v>411310.53442310274</v>
+      </c>
+      <c r="AC100" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>1304</v>
       </c>
@@ -9302,8 +9896,14 @@
       <c r="AA101" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB101" s="1">
+        <v>311806.5</v>
+      </c>
+      <c r="AC101" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>1305</v>
       </c>
@@ -9385,8 +9985,14 @@
       <c r="AA102" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB102" s="1">
+        <v>409065.76207128563</v>
+      </c>
+      <c r="AC102" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>1306</v>
       </c>
@@ -9468,8 +10074,14 @@
       <c r="AA103" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB103" s="1">
+        <v>329270</v>
+      </c>
+      <c r="AC103" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>1307</v>
       </c>
@@ -9551,8 +10163,14 @@
       <c r="AA104" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB104" s="1">
+        <v>357200</v>
+      </c>
+      <c r="AC104" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>1308</v>
       </c>
@@ -9634,8 +10252,14 @@
       <c r="AA105" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB105" s="1">
+        <v>312806.5</v>
+      </c>
+      <c r="AC105" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>1401</v>
       </c>
@@ -9717,8 +10341,14 @@
       <c r="AA106" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB106" s="1">
+        <v>264000</v>
+      </c>
+      <c r="AC106" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>1402</v>
       </c>
@@ -9800,8 +10430,14 @@
       <c r="AA107" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB107" s="1">
+        <v>370782.5</v>
+      </c>
+      <c r="AC107" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>1403</v>
       </c>
@@ -9883,8 +10519,14 @@
       <c r="AA108" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB108" s="1">
+        <v>411759.4888934663</v>
+      </c>
+      <c r="AC108" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>1404</v>
       </c>
@@ -9966,8 +10608,14 @@
       <c r="AA109" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB109" s="1">
+        <v>400535.62713438016</v>
+      </c>
+      <c r="AC109" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>1405</v>
       </c>
@@ -10049,8 +10697,14 @@
       <c r="AA110" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB110" s="1">
+        <v>409514.71654164908</v>
+      </c>
+      <c r="AC110" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>1406</v>
       </c>
@@ -10132,8 +10786,14 @@
       <c r="AA111" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB111" s="1">
+        <v>322710</v>
+      </c>
+      <c r="AC111" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>1407</v>
       </c>
@@ -10215,8 +10875,14 @@
       <c r="AA112" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB112" s="1">
+        <v>336688.35</v>
+      </c>
+      <c r="AC112" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>1408</v>
       </c>
@@ -10298,8 +10964,14 @@
       <c r="AA113" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB113" s="1">
+        <v>370550</v>
+      </c>
+      <c r="AC113" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>1501</v>
       </c>
@@ -10381,8 +11053,14 @@
       <c r="AA114" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB114" s="1">
+        <v>330407</v>
+      </c>
+      <c r="AC114" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>1502</v>
       </c>
@@ -10464,8 +11142,14 @@
       <c r="AA115" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB115" s="1">
+        <v>370000</v>
+      </c>
+      <c r="AC115" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>1503</v>
       </c>
@@ -10547,8 +11231,14 @@
       <c r="AA116" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB116" s="1">
+        <v>318801.02</v>
+      </c>
+      <c r="AC116" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>1504</v>
       </c>
@@ -10630,8 +11320,14 @@
       <c r="AA117" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB117" s="1">
+        <v>404542.73719803535</v>
+      </c>
+      <c r="AC117" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>1505</v>
       </c>
@@ -10713,8 +11409,14 @@
       <c r="AA118" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB118" s="1">
+        <v>319060.34000000003</v>
+      </c>
+      <c r="AC118" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>1506</v>
       </c>
@@ -10796,8 +11498,14 @@
       <c r="AA119" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB119" s="1">
+        <v>313528.5</v>
+      </c>
+      <c r="AC119" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>1507</v>
       </c>
@@ -10879,8 +11587,14 @@
       <c r="AA120" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB120" s="1">
+        <v>319060.34999999998</v>
+      </c>
+      <c r="AC120" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>1508</v>
       </c>
@@ -10960,6 +11674,12 @@
         <v>348166.12</v>
       </c>
       <c r="AA121" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB121" s="1">
+        <v>348166.12</v>
+      </c>
+      <c r="AC121" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/vendas-espelho.xlsx
+++ b/data/vendas-espelho.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1064AAB3-0644-4549-BC9C-578C30321E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{1064AAB3-0644-4549-BC9C-578C30321E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B9B3D30-49C5-4B31-A1D9-E4EEA25F7496}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="91">
   <si>
     <t>Und</t>
   </si>
@@ -680,7 +680,7 @@
     <col min="27" max="27" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -1091,6 +1091,12 @@
       <c r="AC2" t="s">
         <v>1</v>
       </c>
+      <c r="AD2" s="1">
+        <v>330315.8</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -1180,6 +1186,12 @@
       <c r="AC3" t="s">
         <v>1</v>
       </c>
+      <c r="AD3" s="1">
+        <v>297369</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -1269,6 +1281,12 @@
       <c r="AC4" t="s">
         <v>2</v>
       </c>
+      <c r="AD4" s="1">
+        <v>390582.10689519066</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -1358,6 +1376,12 @@
       <c r="AC5" t="s">
         <v>2</v>
       </c>
+      <c r="AD5" s="1">
+        <v>390582.10689519066</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -1447,6 +1471,12 @@
       <c r="AC6" t="s">
         <v>2</v>
       </c>
+      <c r="AD6" s="1">
+        <v>384822.2206716598</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -1536,6 +1566,12 @@
       <c r="AC7" t="s">
         <v>2</v>
       </c>
+      <c r="AD7" s="1">
+        <v>390582.10689519066</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -1625,6 +1661,12 @@
       <c r="AC8" t="s">
         <v>2</v>
       </c>
+      <c r="AD8" s="1">
+        <v>384822.2206716598</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -1714,6 +1756,12 @@
       <c r="AC9" t="s">
         <v>1</v>
       </c>
+      <c r="AD9" s="1">
+        <v>337748.12</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -1803,6 +1851,12 @@
       <c r="AC10" t="s">
         <v>1</v>
       </c>
+      <c r="AD10" s="1">
+        <v>351814.23</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -1892,6 +1946,12 @@
       <c r="AC11" t="s">
         <v>1</v>
       </c>
+      <c r="AD11" s="1">
+        <v>297440.3</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -1981,6 +2041,12 @@
       <c r="AC12" t="s">
         <v>1</v>
       </c>
+      <c r="AD12" s="1">
+        <v>331760.92</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A13">
@@ -2070,6 +2136,12 @@
       <c r="AC13" t="s">
         <v>1</v>
       </c>
+      <c r="AD13" s="1">
+        <v>331038.36</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -2159,6 +2231,12 @@
       <c r="AC14" t="s">
         <v>1</v>
       </c>
+      <c r="AD14" s="1">
+        <v>297708.18</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -2248,6 +2326,12 @@
       <c r="AC15" t="s">
         <v>1</v>
       </c>
+      <c r="AD15" s="1">
+        <v>312549.92</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:87" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -2337,8 +2421,14 @@
       <c r="AC16" t="s">
         <v>1</v>
       </c>
+      <c r="AD16" s="1">
+        <v>301440</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>208</v>
       </c>
@@ -2426,8 +2516,14 @@
       <c r="AC17" t="s">
         <v>1</v>
       </c>
+      <c r="AD17" s="1">
+        <v>298038.75</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>301</v>
       </c>
@@ -2515,8 +2611,14 @@
       <c r="AC18" t="s">
         <v>90</v>
       </c>
+      <c r="AD18" s="1">
+        <v>376741.82444737392</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>302</v>
       </c>
@@ -2604,8 +2706,14 @@
       <c r="AC19" t="s">
         <v>1</v>
       </c>
+      <c r="AD19" s="1">
+        <v>332171.26</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>303</v>
       </c>
@@ -2693,8 +2801,14 @@
       <c r="AC20" t="s">
         <v>1</v>
       </c>
+      <c r="AD20" s="1">
+        <v>332171.26</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>304</v>
       </c>
@@ -2782,8 +2896,14 @@
       <c r="AC21" t="s">
         <v>2</v>
       </c>
+      <c r="AD21" s="1">
+        <v>366249.40015994618</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>305</v>
       </c>
@@ -2871,8 +2991,14 @@
       <c r="AC22" t="s">
         <v>1</v>
       </c>
+      <c r="AD22" s="1">
+        <v>330268.78999999998</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>306</v>
       </c>
@@ -2960,8 +3086,14 @@
       <c r="AC23" t="s">
         <v>90</v>
       </c>
+      <c r="AD23" s="1">
+        <v>366249.40015994618</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>307</v>
       </c>
@@ -3049,8 +3181,14 @@
       <c r="AC24" t="s">
         <v>1</v>
       </c>
+      <c r="AD24" s="1">
+        <v>312960</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>308</v>
       </c>
@@ -3138,8 +3276,14 @@
       <c r="AC25" t="s">
         <v>1</v>
       </c>
+      <c r="AD25" s="1">
+        <v>302905.59999999998</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>401</v>
       </c>
@@ -3227,8 +3371,14 @@
       <c r="AC26" t="s">
         <v>1</v>
       </c>
+      <c r="AD26" s="1">
+        <v>340000</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>402</v>
       </c>
@@ -3316,8 +3466,14 @@
       <c r="AC27" t="s">
         <v>90</v>
       </c>
+      <c r="AD27" s="1">
+        <v>377161.52141887089</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>403</v>
       </c>
@@ -3405,8 +3561,14 @@
       <c r="AC28" t="s">
         <v>1</v>
       </c>
+      <c r="AD28" s="1">
+        <v>325123.86</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>404</v>
       </c>
@@ -3494,8 +3656,14 @@
       <c r="AC29" t="s">
         <v>2</v>
       </c>
+      <c r="AD29" s="1">
+        <v>396280.28959710058</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>405</v>
       </c>
@@ -3583,8 +3751,14 @@
       <c r="AC30" t="s">
         <v>90</v>
       </c>
+      <c r="AD30" s="1">
+        <v>375063.03656138532</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>406</v>
       </c>
@@ -3672,8 +3846,14 @@
       <c r="AC31" t="s">
         <v>2</v>
       </c>
+      <c r="AD31" s="1">
+        <v>392229.96943265648</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>407</v>
       </c>
@@ -3761,8 +3941,14 @@
       <c r="AC32" t="s">
         <v>1</v>
       </c>
+      <c r="AD32" s="1">
+        <v>323268</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>408</v>
       </c>
@@ -3850,8 +4036,14 @@
       <c r="AC33" t="s">
         <v>1</v>
       </c>
+      <c r="AD33" s="1">
+        <v>303262.8</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>501</v>
       </c>
@@ -3939,8 +4131,14 @@
       <c r="AC34" t="s">
         <v>1</v>
       </c>
+      <c r="AD34" s="1">
+        <v>329000</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>502</v>
       </c>
@@ -4028,8 +4226,14 @@
       <c r="AC35" t="s">
         <v>1</v>
       </c>
+      <c r="AD35" s="1">
+        <v>325500</v>
+      </c>
+      <c r="AE35" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>503</v>
       </c>
@@ -4117,8 +4321,14 @@
       <c r="AC36" t="s">
         <v>90</v>
       </c>
+      <c r="AD36" s="1">
+        <v>377581.21839036816</v>
+      </c>
+      <c r="AE36" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>504</v>
       </c>
@@ -4206,8 +4416,14 @@
       <c r="AC37" t="s">
         <v>1</v>
       </c>
+      <c r="AD37" s="1">
+        <v>303620</v>
+      </c>
+      <c r="AE37" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>505</v>
       </c>
@@ -4295,8 +4511,14 @@
       <c r="AC38" t="s">
         <v>1</v>
       </c>
+      <c r="AD38" s="1">
+        <v>310764</v>
+      </c>
+      <c r="AE38" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>506</v>
       </c>
@@ -4384,8 +4606,14 @@
       <c r="AC39" t="s">
         <v>1</v>
       </c>
+      <c r="AD39" s="1">
+        <v>323419.90000000002</v>
+      </c>
+      <c r="AE39" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>507</v>
       </c>
@@ -4473,8 +4701,14 @@
       <c r="AC40" t="s">
         <v>1</v>
       </c>
+      <c r="AD40" s="1">
+        <v>309763.71999999997</v>
+      </c>
+      <c r="AE40" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>508</v>
       </c>
@@ -4562,8 +4796,14 @@
       <c r="AC41" t="s">
         <v>1</v>
       </c>
+      <c r="AD41" s="1">
+        <v>303620</v>
+      </c>
+      <c r="AE41" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>601</v>
       </c>
@@ -4651,8 +4891,14 @@
       <c r="AC42" t="s">
         <v>1</v>
       </c>
+      <c r="AD42" s="1">
+        <v>311260.31</v>
+      </c>
+      <c r="AE42" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>602</v>
       </c>
@@ -4740,8 +4986,14 @@
       <c r="AC43" t="s">
         <v>1</v>
       </c>
+      <c r="AD43" s="1">
+        <v>370514.8</v>
+      </c>
+      <c r="AE43" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>603</v>
       </c>
@@ -4829,8 +5081,14 @@
       <c r="AC44" t="s">
         <v>1</v>
       </c>
+      <c r="AD44" s="1">
+        <v>312907.2</v>
+      </c>
+      <c r="AE44" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>604</v>
       </c>
@@ -4918,8 +5176,14 @@
       <c r="AC45" t="s">
         <v>1</v>
       </c>
+      <c r="AD45" s="1">
+        <v>302977.2</v>
+      </c>
+      <c r="AE45" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>605</v>
       </c>
@@ -5007,8 +5271,14 @@
       <c r="AC46" t="s">
         <v>1</v>
       </c>
+      <c r="AD46" s="1">
+        <v>370674.7</v>
+      </c>
+      <c r="AE46" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>606</v>
       </c>
@@ -5096,8 +5366,14 @@
       <c r="AC47" t="s">
         <v>1</v>
       </c>
+      <c r="AD47" s="1">
+        <v>323380</v>
+      </c>
+      <c r="AE47" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>607</v>
       </c>
@@ -5185,8 +5461,14 @@
       <c r="AC48" t="s">
         <v>1</v>
       </c>
+      <c r="AD48" s="1">
+        <v>311121.2</v>
+      </c>
+      <c r="AE48" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>608</v>
       </c>
@@ -5274,8 +5556,14 @@
       <c r="AC49" t="s">
         <v>90</v>
       </c>
+      <c r="AD49" s="1">
+        <v>367508.49107443745</v>
+      </c>
+      <c r="AE49" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>701</v>
       </c>
@@ -5363,8 +5651,14 @@
       <c r="AC50" t="s">
         <v>1</v>
       </c>
+      <c r="AD50" s="1">
+        <v>311615.64</v>
+      </c>
+      <c r="AE50" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>702</v>
       </c>
@@ -5452,8 +5746,14 @@
       <c r="AC51" t="s">
         <v>1</v>
       </c>
+      <c r="AD51" s="1">
+        <v>364345.22</v>
+      </c>
+      <c r="AE51" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>703</v>
       </c>
@@ -5541,8 +5841,14 @@
       <c r="AC52" t="s">
         <v>1</v>
       </c>
+      <c r="AD52" s="1">
+        <v>311615.64</v>
+      </c>
+      <c r="AE52" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>704</v>
       </c>
@@ -5630,8 +5936,14 @@
       <c r="AC53" t="s">
         <v>2</v>
       </c>
+      <c r="AD53" s="1">
+        <v>393576.83284374687</v>
+      </c>
+      <c r="AE53" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>705</v>
       </c>
@@ -5719,8 +6031,14 @@
       <c r="AC54" t="s">
         <v>1</v>
       </c>
+      <c r="AD54" s="1">
+        <v>312314.15999999997</v>
+      </c>
+      <c r="AE54" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>706</v>
       </c>
@@ -5808,8 +6126,14 @@
       <c r="AC55" t="s">
         <v>2</v>
       </c>
+      <c r="AD55" s="1">
+        <v>393576.83284374687</v>
+      </c>
+      <c r="AE55" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>707</v>
       </c>
@@ -5897,8 +6221,14 @@
       <c r="AC56" t="s">
         <v>90</v>
       </c>
+      <c r="AD56" s="1">
+        <v>376322.12747587671</v>
+      </c>
+      <c r="AE56" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>708</v>
       </c>
@@ -5986,8 +6316,14 @@
       <c r="AC57" t="s">
         <v>1</v>
       </c>
+      <c r="AD57" s="1">
+        <v>303570.15000000002</v>
+      </c>
+      <c r="AE57" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>801</v>
       </c>
@@ -6075,8 +6411,14 @@
       <c r="AC58" t="s">
         <v>1</v>
       </c>
+      <c r="AD58" s="1">
+        <v>311970.98</v>
+      </c>
+      <c r="AE58" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>802</v>
       </c>
@@ -6164,8 +6506,14 @@
       <c r="AC59" t="s">
         <v>1</v>
       </c>
+      <c r="AD59" s="1">
+        <v>375540.19</v>
+      </c>
+      <c r="AE59" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>803</v>
       </c>
@@ -6253,8 +6601,14 @@
       <c r="AC60" t="s">
         <v>1</v>
       </c>
+      <c r="AD60" s="1">
+        <v>312621.65000000002</v>
+      </c>
+      <c r="AE60" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>804</v>
       </c>
@@ -6342,8 +6696,14 @@
       <c r="AC61" t="s">
         <v>90</v>
       </c>
+      <c r="AD61" s="1">
+        <v>368347.88501743157</v>
+      </c>
+      <c r="AE61" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>805</v>
       </c>
@@ -6431,8 +6791,14 @@
       <c r="AC62" t="s">
         <v>1</v>
       </c>
+      <c r="AD62" s="1">
+        <v>311835.59999999998</v>
+      </c>
+      <c r="AE62" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>806</v>
       </c>
@@ -6520,8 +6886,14 @@
       <c r="AC63" t="s">
         <v>2</v>
       </c>
+      <c r="AD63" s="1">
+        <v>368347.88501743157</v>
+      </c>
+      <c r="AE63" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>807</v>
       </c>
@@ -6609,8 +6981,14 @@
       <c r="AC64" t="s">
         <v>1</v>
       </c>
+      <c r="AD64" s="1">
+        <v>332171.27</v>
+      </c>
+      <c r="AE64" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>808</v>
       </c>
@@ -6698,8 +7076,14 @@
       <c r="AC65" t="s">
         <v>1</v>
       </c>
+      <c r="AD65" s="1">
+        <v>304691.59999999998</v>
+      </c>
+      <c r="AE65" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>901</v>
       </c>
@@ -6787,8 +7171,14 @@
       <c r="AC66" t="s">
         <v>90</v>
       </c>
+      <c r="AD66" s="1">
+        <v>382407.73356258462</v>
+      </c>
+      <c r="AE66" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>902</v>
       </c>
@@ -6876,8 +7266,14 @@
       <c r="AC67" t="s">
         <v>1</v>
       </c>
+      <c r="AD67" s="1">
+        <v>290000</v>
+      </c>
+      <c r="AE67" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>903</v>
       </c>
@@ -6965,8 +7361,14 @@
       <c r="AC68" t="s">
         <v>1</v>
       </c>
+      <c r="AD68" s="1">
+        <v>338158.2</v>
+      </c>
+      <c r="AE68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>904</v>
       </c>
@@ -7054,8 +7456,14 @@
       <c r="AC69" t="s">
         <v>2</v>
       </c>
+      <c r="AD69" s="1">
+        <v>371915.30927515705</v>
+      </c>
+      <c r="AE69" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>905</v>
       </c>
@@ -7143,8 +7551,14 @@
       <c r="AC70" t="s">
         <v>2</v>
       </c>
+      <c r="AD70" s="1">
+        <v>406820.98971946858</v>
+      </c>
+      <c r="AE70" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>906</v>
       </c>
@@ -7232,8 +7646,14 @@
       <c r="AC71" t="s">
         <v>2</v>
       </c>
+      <c r="AD71" s="1">
+        <v>397841.90031219955</v>
+      </c>
+      <c r="AE71" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>907</v>
       </c>
@@ -7321,8 +7741,14 @@
       <c r="AC72" t="s">
         <v>1</v>
       </c>
+      <c r="AD72" s="1">
+        <v>311121.2</v>
+      </c>
+      <c r="AE72" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>908</v>
       </c>
@@ -7410,8 +7836,14 @@
       <c r="AC73" t="s">
         <v>1</v>
       </c>
+      <c r="AD73" s="1">
+        <v>307727.76</v>
+      </c>
+      <c r="AE73" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1001</v>
       </c>
@@ -7499,8 +7931,14 @@
       <c r="AC74" t="s">
         <v>1</v>
       </c>
+      <c r="AD74" s="1">
+        <v>320387.5</v>
+      </c>
+      <c r="AE74" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1002</v>
       </c>
@@ -7588,8 +8026,14 @@
       <c r="AC75" t="s">
         <v>1</v>
       </c>
+      <c r="AD75" s="1">
+        <v>274525</v>
+      </c>
+      <c r="AE75" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1003</v>
       </c>
@@ -7677,8 +8121,14 @@
       <c r="AC76" t="s">
         <v>1</v>
       </c>
+      <c r="AD76" s="1">
+        <v>360355.93</v>
+      </c>
+      <c r="AE76" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1004</v>
       </c>
@@ -7766,8 +8216,14 @@
       <c r="AC77" t="s">
         <v>1</v>
       </c>
+      <c r="AD77" s="1">
+        <v>310493</v>
+      </c>
+      <c r="AE77" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1005</v>
       </c>
@@ -7855,8 +8311,14 @@
       <c r="AC78" t="s">
         <v>1</v>
       </c>
+      <c r="AD78" s="1">
+        <v>347641.85</v>
+      </c>
+      <c r="AE78" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1006</v>
       </c>
@@ -7944,8 +8406,14 @@
       <c r="AC79" t="s">
         <v>2</v>
       </c>
+      <c r="AD79" s="1">
+        <v>398515.33201774483</v>
+      </c>
+      <c r="AE79" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1007</v>
       </c>
@@ -8033,8 +8501,14 @@
       <c r="AC80" t="s">
         <v>1</v>
       </c>
+      <c r="AD80" s="1">
+        <v>360000</v>
+      </c>
+      <c r="AE80" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1008</v>
       </c>
@@ -8122,8 +8596,14 @@
       <c r="AC81" t="s">
         <v>90</v>
       </c>
+      <c r="AD81" s="1">
+        <v>372544.85473240277</v>
+      </c>
+      <c r="AE81" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1101</v>
       </c>
@@ -8211,8 +8691,14 @@
       <c r="AC82" t="s">
         <v>1</v>
       </c>
+      <c r="AD82" s="1">
+        <v>274525</v>
+      </c>
+      <c r="AE82" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1102</v>
       </c>
@@ -8300,8 +8786,14 @@
       <c r="AC83" t="s">
         <v>1</v>
       </c>
+      <c r="AD83" s="1">
+        <v>338400</v>
+      </c>
+      <c r="AE83" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1103</v>
       </c>
@@ -8389,8 +8881,14 @@
       <c r="AC84" t="s">
         <v>2</v>
       </c>
+      <c r="AD84" s="1">
+        <v>410412.62548237591</v>
+      </c>
+      <c r="AE84" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1104</v>
       </c>
@@ -8478,8 +8976,14 @@
       <c r="AC85" t="s">
         <v>90</v>
       </c>
+      <c r="AD85" s="1">
+        <v>373174.40018964838</v>
+      </c>
+      <c r="AE85" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1105</v>
       </c>
@@ -8567,8 +9071,14 @@
       <c r="AC86" t="s">
         <v>2</v>
       </c>
+      <c r="AD86" s="1">
+        <v>399434.88083385822</v>
+      </c>
+      <c r="AE86" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1106</v>
       </c>
@@ -8656,8 +9166,14 @@
       <c r="AC87" t="s">
         <v>2</v>
       </c>
+      <c r="AD87" s="1">
+        <v>399188.76372328994</v>
+      </c>
+      <c r="AE87" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1107</v>
       </c>
@@ -8745,8 +9261,14 @@
       <c r="AC88" t="s">
         <v>1</v>
       </c>
+      <c r="AD88" s="1">
+        <v>357200</v>
+      </c>
+      <c r="AE88" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>1108</v>
       </c>
@@ -8834,8 +9356,14 @@
       <c r="AC89" t="s">
         <v>1</v>
       </c>
+      <c r="AD89" s="1">
+        <v>370120</v>
+      </c>
+      <c r="AE89" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>1201</v>
       </c>
@@ -8923,8 +9451,14 @@
       <c r="AC90" t="s">
         <v>1</v>
       </c>
+      <c r="AD90" s="1">
+        <v>358027</v>
+      </c>
+      <c r="AE90" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>1202</v>
       </c>
@@ -9012,8 +9546,14 @@
       <c r="AC91" t="s">
         <v>1</v>
       </c>
+      <c r="AD91" s="1">
+        <v>338400</v>
+      </c>
+      <c r="AE91" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1203</v>
       </c>
@@ -9101,8 +9641,14 @@
       <c r="AC92" t="s">
         <v>2</v>
       </c>
+      <c r="AD92" s="1">
+        <v>410861.57995273953</v>
+      </c>
+      <c r="AE92" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1204</v>
       </c>
@@ -9190,8 +9736,14 @@
       <c r="AC93" t="s">
         <v>1</v>
       </c>
+      <c r="AD93" s="1">
+        <v>312445.5</v>
+      </c>
+      <c r="AE93" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>1205</v>
       </c>
@@ -9279,8 +9831,14 @@
       <c r="AC94" t="s">
         <v>90</v>
       </c>
+      <c r="AD94" s="1">
+        <v>381988.0365910877</v>
+      </c>
+      <c r="AE94" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>1206</v>
       </c>
@@ -9368,8 +9926,14 @@
       <c r="AC95" t="s">
         <v>1</v>
       </c>
+      <c r="AD95" s="1">
+        <v>312445.5</v>
+      </c>
+      <c r="AE95" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>1207</v>
       </c>
@@ -9457,8 +10021,14 @@
       <c r="AC96" t="s">
         <v>1</v>
       </c>
+      <c r="AD96" s="1">
+        <v>336490</v>
+      </c>
+      <c r="AE96" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>1208</v>
       </c>
@@ -9546,8 +10116,14 @@
       <c r="AC97" t="s">
         <v>1</v>
       </c>
+      <c r="AD97" s="1">
+        <v>370596.7</v>
+      </c>
+      <c r="AE97" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1301</v>
       </c>
@@ -9635,8 +10211,14 @@
       <c r="AC98" t="s">
         <v>1</v>
       </c>
+      <c r="AD98" s="1">
+        <v>264000</v>
+      </c>
+      <c r="AE98" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>1302</v>
       </c>
@@ -9724,8 +10306,14 @@
       <c r="AC99" t="s">
         <v>1</v>
       </c>
+      <c r="AD99" s="1">
+        <v>296695.15000000002</v>
+      </c>
+      <c r="AE99" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>1303</v>
       </c>
@@ -9813,8 +10401,14 @@
       <c r="AC100" t="s">
         <v>2</v>
       </c>
+      <c r="AD100" s="1">
+        <v>411310.53442310274</v>
+      </c>
+      <c r="AE100" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>1304</v>
       </c>
@@ -9902,8 +10496,14 @@
       <c r="AC101" t="s">
         <v>1</v>
       </c>
+      <c r="AD101" s="1">
+        <v>311806.5</v>
+      </c>
+      <c r="AE101" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>1305</v>
       </c>
@@ -9991,8 +10591,14 @@
       <c r="AC102" t="s">
         <v>2</v>
       </c>
+      <c r="AD102" s="1">
+        <v>409065.76207128563</v>
+      </c>
+      <c r="AE102" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>1306</v>
       </c>
@@ -10080,8 +10686,14 @@
       <c r="AC103" t="s">
         <v>1</v>
       </c>
+      <c r="AD103" s="1">
+        <v>329270</v>
+      </c>
+      <c r="AE103" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>1307</v>
       </c>
@@ -10169,8 +10781,14 @@
       <c r="AC104" t="s">
         <v>1</v>
       </c>
+      <c r="AD104" s="1">
+        <v>357200</v>
+      </c>
+      <c r="AE104" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>1308</v>
       </c>
@@ -10258,8 +10876,14 @@
       <c r="AC105" t="s">
         <v>1</v>
       </c>
+      <c r="AD105" s="1">
+        <v>312806.5</v>
+      </c>
+      <c r="AE105" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>1401</v>
       </c>
@@ -10347,8 +10971,14 @@
       <c r="AC106" t="s">
         <v>1</v>
       </c>
+      <c r="AD106" s="1">
+        <v>264000</v>
+      </c>
+      <c r="AE106" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>1402</v>
       </c>
@@ -10436,8 +11066,14 @@
       <c r="AC107" t="s">
         <v>1</v>
       </c>
+      <c r="AD107" s="1">
+        <v>370782.5</v>
+      </c>
+      <c r="AE107" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>1403</v>
       </c>
@@ -10525,8 +11161,14 @@
       <c r="AC108" t="s">
         <v>2</v>
       </c>
+      <c r="AD108" s="1">
+        <v>411759.4888934663</v>
+      </c>
+      <c r="AE108" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>1404</v>
       </c>
@@ -10614,8 +11256,14 @@
       <c r="AC109" t="s">
         <v>2</v>
       </c>
+      <c r="AD109" s="1">
+        <v>400535.62713438016</v>
+      </c>
+      <c r="AE109" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>1405</v>
       </c>
@@ -10703,8 +11351,14 @@
       <c r="AC110" t="s">
         <v>2</v>
       </c>
+      <c r="AD110" s="1">
+        <v>390533.14</v>
+      </c>
+      <c r="AE110" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="111" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>1406</v>
       </c>
@@ -10792,8 +11446,14 @@
       <c r="AC111" t="s">
         <v>1</v>
       </c>
+      <c r="AD111" s="1">
+        <v>322710</v>
+      </c>
+      <c r="AE111" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>1407</v>
       </c>
@@ -10881,8 +11541,14 @@
       <c r="AC112" t="s">
         <v>1</v>
       </c>
+      <c r="AD112" s="1">
+        <v>336688.35</v>
+      </c>
+      <c r="AE112" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="113" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>1408</v>
       </c>
@@ -10970,8 +11636,14 @@
       <c r="AC113" t="s">
         <v>1</v>
       </c>
+      <c r="AD113" s="1">
+        <v>370550</v>
+      </c>
+      <c r="AE113" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="114" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>1501</v>
       </c>
@@ -11059,8 +11731,14 @@
       <c r="AC114" t="s">
         <v>1</v>
       </c>
+      <c r="AD114" s="1">
+        <v>330407</v>
+      </c>
+      <c r="AE114" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="115" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>1502</v>
       </c>
@@ -11148,8 +11826,14 @@
       <c r="AC115" t="s">
         <v>1</v>
       </c>
+      <c r="AD115" s="1">
+        <v>370000</v>
+      </c>
+      <c r="AE115" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="116" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>1503</v>
       </c>
@@ -11237,8 +11921,14 @@
       <c r="AC116" t="s">
         <v>1</v>
       </c>
+      <c r="AD116" s="1">
+        <v>318801.02</v>
+      </c>
+      <c r="AE116" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="117" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>1504</v>
       </c>
@@ -11326,8 +12016,14 @@
       <c r="AC117" t="s">
         <v>2</v>
       </c>
+      <c r="AD117" s="1">
+        <v>404542.73719803535</v>
+      </c>
+      <c r="AE117" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="118" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>1505</v>
       </c>
@@ -11415,8 +12111,14 @@
       <c r="AC118" t="s">
         <v>1</v>
       </c>
+      <c r="AD118" s="1">
+        <v>319060.34000000003</v>
+      </c>
+      <c r="AE118" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="119" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>1506</v>
       </c>
@@ -11504,8 +12206,14 @@
       <c r="AC119" t="s">
         <v>1</v>
       </c>
+      <c r="AD119" s="1">
+        <v>313528.5</v>
+      </c>
+      <c r="AE119" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="120" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>1507</v>
       </c>
@@ -11593,8 +12301,14 @@
       <c r="AC120" t="s">
         <v>1</v>
       </c>
+      <c r="AD120" s="1">
+        <v>319060.34999999998</v>
+      </c>
+      <c r="AE120" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="121" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>1508</v>
       </c>
@@ -11680,6 +12394,12 @@
         <v>348166.12</v>
       </c>
       <c r="AC121" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD121" s="1">
+        <v>348166.12</v>
+      </c>
+      <c r="AE121" t="s">
         <v>1</v>
       </c>
     </row>
